--- a/model/Outputs/11. Interest rate/0/Output Files/0.1/Output_18_47.xlsx
+++ b/model/Outputs/11. Interest rate/0/Output Files/0.1/Output_18_47.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5717662.902390702</v>
+        <v>5717790.953753834</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13052476.69608441</v>
+        <v>13052476.69608428</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13052476.69608441</v>
+        <v>13052476.69608428</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1002742.51642604</v>
+        <v>1002742.516425933</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1002742.51642604</v>
+        <v>1002742.516425933</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>39020031.84654358</v>
+        <v>39020031.84654368</v>
       </c>
     </row>
   </sheetData>
@@ -711,10 +711,10 @@
         <v>178.4965164019308</v>
       </c>
       <c r="U2" t="n">
-        <v>217.9130412595499</v>
+        <v>242.1997488099172</v>
       </c>
       <c r="V2" t="n">
-        <v>222.8510241668239</v>
+        <v>198.5643166164567</v>
       </c>
       <c r="W2" t="n">
         <v>231.3734759809475</v>
@@ -736,7 +736,7 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>65.17276219783516</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -751,7 +751,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>330.7762569977419</v>
       </c>
       <c r="I3" t="n">
         <v>212.1645934385184</v>
@@ -781,10 +781,10 @@
         <v>154.6833405621777</v>
       </c>
       <c r="R3" t="n">
-        <v>238.1623164525984</v>
+        <v>131.3261369150208</v>
       </c>
       <c r="S3" t="n">
-        <v>346</v>
+        <v>56.88716034196977</v>
       </c>
       <c r="T3" t="n">
         <v>346</v>
@@ -845,10 +845,10 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>91.96496727492936</v>
+        <v>94.69257861566462</v>
       </c>
       <c r="N4" t="n">
-        <v>145.6963703536521</v>
+        <v>142.9687590129169</v>
       </c>
       <c r="O4" t="n">
         <v>216.3682526036051</v>
@@ -897,7 +897,7 @@
         <v>42.47457824299391</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>3.339155739849787</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -942,13 +942,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>81.71042910885558</v>
+        <v>81.71042910885556</v>
       </c>
       <c r="T5" t="n">
-        <v>178.4965164019308</v>
+        <v>154.2098088515635</v>
       </c>
       <c r="U5" t="n">
-        <v>221.2521969993997</v>
+        <v>242.1997488099172</v>
       </c>
       <c r="V5" t="n">
         <v>222.8510241668239</v>
@@ -976,7 +976,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>80.4886136365115</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>342.6720972219126</v>
@@ -1021,13 +1021,13 @@
         <v>131.3261369150208</v>
       </c>
       <c r="S6" t="n">
-        <v>56.88716034196977</v>
+        <v>56.88716034196979</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>80.48861363650013</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>346</v>
       </c>
       <c r="V6" t="n">
         <v>7.510667191520156</v>
@@ -1039,7 +1039,7 @@
         <v>12.86273944538755</v>
       </c>
       <c r="Y6" t="n">
-        <v>346</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1082,13 +1082,13 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>91.96496727492936</v>
+        <v>94.69257861566464</v>
       </c>
       <c r="N7" t="n">
         <v>145.6963703536521</v>
       </c>
       <c r="O7" t="n">
-        <v>216.3682526036051</v>
+        <v>213.6406412628698</v>
       </c>
       <c r="P7" t="n">
         <v>265.835307164343</v>
@@ -1134,7 +1134,7 @@
         <v>42.47457824299391</v>
       </c>
       <c r="D8" t="n">
-        <v>3.339155739849787</v>
+        <v>2.337248189482466</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -1179,10 +1179,10 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>80.70852155848823</v>
+        <v>81.71042910885556</v>
       </c>
       <c r="T8" t="n">
-        <v>178.4965164019308</v>
+        <v>178.4965164019307</v>
       </c>
       <c r="U8" t="n">
         <v>242.1997488099172</v>
@@ -1210,13 +1210,13 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>67.23073339150105</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
-        <v>218.0504645274926</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1255,22 +1255,22 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>352</v>
+        <v>131.3261369150208</v>
       </c>
       <c r="S9" t="n">
-        <v>56.88716034196977</v>
+        <v>56.88716034196979</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>352.0000000000069</v>
       </c>
       <c r="V9" t="n">
-        <v>352</v>
+        <v>7.510667191520156</v>
       </c>
       <c r="W9" t="n">
-        <v>352</v>
+        <v>25.37314290982852</v>
       </c>
       <c r="X9" t="n">
         <v>12.86273944538755</v>
@@ -1319,7 +1319,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>94.69257861566462</v>
+        <v>94.69257861566464</v>
       </c>
       <c r="N10" t="n">
         <v>145.6963703536521</v>
@@ -1365,25 +1365,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>81.99931295557451</v>
+        <v>25.06047877771288</v>
       </c>
       <c r="C11" t="n">
-        <v>7.238189411782114</v>
+        <v>49.47457824299391</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>10.33915573984979</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>4.363289606868648</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>3.488025553347868</v>
+        <v>3.488025553347882</v>
       </c>
       <c r="H11" t="n">
-        <v>5.251211467346504</v>
+        <v>5.251211467346479</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1416,10 +1416,10 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>88.71042910885556</v>
+        <v>88.71042910885558</v>
       </c>
       <c r="T11" t="n">
-        <v>185.4965164019307</v>
+        <v>185.4965164019308</v>
       </c>
       <c r="U11" t="n">
         <v>249.1997488099172</v>
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>359</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -1453,7 +1453,7 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>68.61645072102425</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -1462,7 +1462,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>330.7762569977419</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1489,22 +1489,22 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>154.6833405621777</v>
       </c>
       <c r="R12" t="n">
-        <v>138.3261369150208</v>
+        <v>359.0000000000173</v>
       </c>
       <c r="S12" t="n">
-        <v>63.88716034196979</v>
+        <v>359.0000000000182</v>
       </c>
       <c r="T12" t="n">
-        <v>359</v>
+        <v>4.776887859023248</v>
       </c>
       <c r="U12" t="n">
-        <v>0.200878628111276</v>
+        <v>0.2008786281112975</v>
       </c>
       <c r="V12" t="n">
-        <v>359</v>
+        <v>14.51066719152016</v>
       </c>
       <c r="W12" t="n">
         <v>32.37314290982852</v>
@@ -1513,7 +1513,7 @@
         <v>19.86273944538755</v>
       </c>
       <c r="Y12" t="n">
-        <v>12.15030607453207</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1553,7 +1553,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>5.585037993844747</v>
+        <v>5.585037993844765</v>
       </c>
       <c r="M13" t="n">
         <v>101.6925786156646</v>
@@ -1617,10 +1617,10 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G14" t="n">
-        <v>3.488025553347882</v>
+        <v>3.488025553347868</v>
       </c>
       <c r="H14" t="n">
-        <v>5.251211467346479</v>
+        <v>5.251211467346504</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1653,19 +1653,19 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>88.71042910885558</v>
+        <v>88.71042910885556</v>
       </c>
       <c r="T14" t="n">
-        <v>185.4965164019308</v>
+        <v>185.4965164019307</v>
       </c>
       <c r="U14" t="n">
-        <v>187.3712859239749</v>
+        <v>249.1997488099172</v>
       </c>
       <c r="V14" t="n">
         <v>229.8510241668239</v>
       </c>
       <c r="W14" t="n">
-        <v>238.3734759809475</v>
+        <v>176.5450130950727</v>
       </c>
       <c r="X14" t="n">
         <v>192.2818334606677</v>
@@ -1690,7 +1690,7 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -1729,25 +1729,25 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>138.3261369150208</v>
+        <v>359.0000000000119</v>
       </c>
       <c r="S15" t="n">
-        <v>97.71744144845655</v>
+        <v>209.7875941005787</v>
       </c>
       <c r="T15" t="n">
-        <v>359</v>
+        <v>4.776887859023249</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2008786281112975</v>
+        <v>359.0000000000101</v>
       </c>
       <c r="V15" t="n">
-        <v>14.51066719152016</v>
+        <v>359.0000000000101</v>
       </c>
       <c r="W15" t="n">
         <v>32.37314290982852</v>
       </c>
       <c r="X15" t="n">
-        <v>359</v>
+        <v>19.86273944538755</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
@@ -1790,7 +1790,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>5.585037993844765</v>
+        <v>5.585037993844747</v>
       </c>
       <c r="M16" t="n">
         <v>101.6925786156646</v>
@@ -1857,7 +1857,7 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.251211467346504</v>
+        <v>1.251211467346479</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -1890,10 +1890,10 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>78.8717779314301</v>
+        <v>84.71042910885558</v>
       </c>
       <c r="T17" t="n">
-        <v>181.4965164019307</v>
+        <v>181.4965164019308</v>
       </c>
       <c r="U17" t="n">
         <v>245.1997488099172</v>
@@ -1908,7 +1908,7 @@
         <v>188.2818334606677</v>
       </c>
       <c r="Y17" t="n">
-        <v>107.3174326828064</v>
+        <v>101.4787815054472</v>
       </c>
     </row>
     <row r="18">
@@ -1921,10 +1921,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>359</v>
+        <v>63.81760319460771</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E18" t="n">
         <v>342.6720972219126</v>
@@ -1969,16 +1969,16 @@
         <v>134.3261369150208</v>
       </c>
       <c r="S18" t="n">
-        <v>59.88716034196979</v>
+        <v>59.88716034196977</v>
       </c>
       <c r="T18" t="n">
-        <v>0.7768878590232496</v>
+        <v>0.7768878590232475</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>63.26595728383083</v>
+        <v>10.51066719152016</v>
       </c>
       <c r="W18" t="n">
         <v>28.37314290982852</v>
@@ -2027,10 +2027,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1.585037993844747</v>
+        <v>1.585037993844765</v>
       </c>
       <c r="M19" t="n">
-        <v>97.69257861566464</v>
+        <v>97.69257861566462</v>
       </c>
       <c r="N19" t="n">
         <v>148.6963703536521</v>
@@ -2088,13 +2088,13 @@
         <v>0.3632896068686478</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8896287080118555</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5017861551637537</v>
+        <v>1.251211467346504</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2127,7 +2127,7 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>79.62120324360757</v>
+        <v>79.76140663950399</v>
       </c>
       <c r="T20" t="n">
         <v>181.4965164019307</v>
@@ -2158,13 +2158,13 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>359</v>
+        <v>359.0000000000101</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E21" t="n">
-        <v>342.6720972219126</v>
+        <v>47.48970041651026</v>
       </c>
       <c r="F21" t="n">
         <v>339.6362423378769</v>
@@ -2212,7 +2212,7 @@
         <v>0.7768878590232496</v>
       </c>
       <c r="U21" t="n">
-        <v>52.75529009231057</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
         <v>10.51066719152016</v>
@@ -2325,13 +2325,13 @@
         <v>0.3632896068686478</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>0.8896287080118555</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.251211467346479</v>
+        <v>1.251211467346504</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -2364,13 +2364,13 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>84.71042910885558</v>
+        <v>78.87177793149381</v>
       </c>
       <c r="T23" t="n">
-        <v>181.4965164019308</v>
+        <v>181.4965164019307</v>
       </c>
       <c r="U23" t="n">
-        <v>240.2507263405032</v>
+        <v>245.1997488099172</v>
       </c>
       <c r="V23" t="n">
         <v>225.8510241668239</v>
@@ -2398,16 +2398,16 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E24" t="n">
-        <v>69.83196464674286</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F24" t="n">
-        <v>339.6362423378769</v>
+        <v>248.770504970307</v>
       </c>
       <c r="G24" t="n">
-        <v>325.5954226674802</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -2437,16 +2437,16 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>154.6833405621777</v>
       </c>
       <c r="R24" t="n">
         <v>134.3261369150208</v>
       </c>
       <c r="S24" t="n">
-        <v>59.88716034196977</v>
+        <v>59.88716034196979</v>
       </c>
       <c r="T24" t="n">
-        <v>0.7768878590232475</v>
+        <v>0.7768878590232496</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
@@ -2461,7 +2461,7 @@
         <v>15.86273944538755</v>
       </c>
       <c r="Y24" t="n">
-        <v>359</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2501,10 +2501,10 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>1.585037993844765</v>
+        <v>1.585037993844747</v>
       </c>
       <c r="M25" t="n">
-        <v>97.69257861566462</v>
+        <v>97.69257861566464</v>
       </c>
       <c r="N25" t="n">
         <v>148.6963703536521</v>
@@ -2562,13 +2562,13 @@
         <v>48.36328960686865</v>
       </c>
       <c r="F26" t="n">
-        <v>48.88962870801186</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>47.48802555334788</v>
       </c>
       <c r="H26" t="n">
-        <v>39.39026845545563</v>
+        <v>49.25121146734648</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2601,13 +2601,13 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>89.94017747639882</v>
       </c>
       <c r="T26" t="n">
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>293.1997488099172</v>
       </c>
       <c r="V26" t="n">
         <v>273.8510241668239</v>
@@ -2616,10 +2616,10 @@
         <v>282.3734759809475</v>
       </c>
       <c r="X26" t="n">
-        <v>236.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>155.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -2632,7 +2632,7 @@
         <v>28.55655664632661</v>
       </c>
       <c r="C27" t="n">
-        <v>5.099912445519294</v>
+        <v>350.0000000000152</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -2641,13 +2641,13 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>275.0281864229991</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -2677,10 +2677,10 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>350</v>
+        <v>182.6046961886564</v>
       </c>
       <c r="S27" t="n">
-        <v>350</v>
+        <v>107.8871603419698</v>
       </c>
       <c r="T27" t="n">
         <v>48.77688785902325</v>
@@ -2738,25 +2738,25 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>49.58503799384476</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>145.6925786156646</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>196.6963703536521</v>
+        <v>69.8085179062839</v>
       </c>
       <c r="O28" t="n">
         <v>267.3682526036051</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>316.835307164343</v>
       </c>
       <c r="Q28" t="n">
-        <v>350</v>
+        <v>350.0000000000152</v>
       </c>
       <c r="R28" t="n">
-        <v>344.669838107427</v>
+        <v>350.0000000000152</v>
       </c>
       <c r="S28" t="n">
         <v>4.267922325806239</v>
@@ -2787,19 +2787,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>119.9993129555745</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>48.33915573984979</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>42.88962870801186</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -2838,13 +2838,13 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>126.7104291088556</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>223.4965164019307</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>35.91013245811831</v>
+        <v>287.1997488099172</v>
       </c>
       <c r="V29" t="n">
         <v>267.8510241668239</v>
@@ -2853,7 +2853,7 @@
         <v>276.3734759809475</v>
       </c>
       <c r="X29" t="n">
-        <v>230.2818334606677</v>
+        <v>214.6493766959871</v>
       </c>
       <c r="Y29" t="n">
         <v>149.3174326828064</v>
@@ -2866,7 +2866,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>350</v>
+        <v>22.55655664632661</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
@@ -2875,19 +2875,19 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>70.46644739187306</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>330.7762569977419</v>
       </c>
       <c r="I30" t="n">
-        <v>212.1645934385184</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2911,7 +2911,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>154.6833405621777</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>176.3261369150208</v>
@@ -2926,7 +2926,7 @@
         <v>38.20087862811128</v>
       </c>
       <c r="V30" t="n">
-        <v>102.1340914486787</v>
+        <v>52.51066719152016</v>
       </c>
       <c r="W30" t="n">
         <v>70.37314290982852</v>
@@ -2975,13 +2975,13 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>43.58503799384475</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>139.6925786156646</v>
+        <v>86.07644023209018</v>
       </c>
       <c r="N31" t="n">
-        <v>190.6963703536521</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>261.3682526036051</v>
@@ -2990,10 +2990,10 @@
         <v>310.835307164343</v>
       </c>
       <c r="Q31" t="n">
-        <v>350</v>
+        <v>350.0000000000153</v>
       </c>
       <c r="R31" t="n">
-        <v>62.10245326889032</v>
+        <v>350.0000000000153</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -3081,13 +3081,13 @@
         <v>175.4965164019307</v>
       </c>
       <c r="U32" t="n">
-        <v>239.1997488099172</v>
+        <v>237.1514412596185</v>
       </c>
       <c r="V32" t="n">
         <v>219.8510241668239</v>
       </c>
       <c r="W32" t="n">
-        <v>226.3251684305802</v>
+        <v>228.3734759809475</v>
       </c>
       <c r="X32" t="n">
         <v>182.2818334606677</v>
@@ -3103,7 +3103,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>344</v>
+        <v>0</v>
       </c>
       <c r="C33" t="n">
         <v>0</v>
@@ -3115,13 +3115,13 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>330.7762569977419</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -3151,13 +3151,13 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>128.3261369150208</v>
+        <v>270.6124081154683</v>
       </c>
       <c r="S33" t="n">
-        <v>53.88716034196979</v>
+        <v>344.0000000000146</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>344.0000000000146</v>
       </c>
       <c r="U33" t="n">
         <v>0</v>
@@ -3169,10 +3169,10 @@
         <v>22.37314290982852</v>
       </c>
       <c r="X33" t="n">
-        <v>107.1218356439186</v>
+        <v>9.862739445387547</v>
       </c>
       <c r="Y33" t="n">
-        <v>344</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -3312,7 +3312,7 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>73.83567729833818</v>
+        <v>75.71042910885556</v>
       </c>
       <c r="T35" t="n">
         <v>172.4965164019307</v>
@@ -3330,7 +3330,7 @@
         <v>179.2818334606677</v>
       </c>
       <c r="Y35" t="n">
-        <v>98.31743268280638</v>
+        <v>96.44268087228882</v>
       </c>
     </row>
     <row r="36">
@@ -3349,13 +3349,13 @@
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>337</v>
       </c>
       <c r="F36" t="n">
-        <v>6.031296672775588</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>325.5954226674802</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -3388,16 +3388,16 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>337</v>
+        <v>125.3261369150208</v>
       </c>
       <c r="S36" t="n">
-        <v>50.88716034196979</v>
+        <v>279.9968974322444</v>
       </c>
       <c r="T36" t="n">
-        <v>337</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>337</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
         <v>1.510667191520156</v>
@@ -3452,13 +3452,13 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>87.037767275077</v>
+        <v>88.69257861566464</v>
       </c>
       <c r="N37" t="n">
         <v>139.6963703536521</v>
       </c>
       <c r="O37" t="n">
-        <v>210.3682526036051</v>
+        <v>208.7134412628697</v>
       </c>
       <c r="P37" t="n">
         <v>259.835307164343</v>
@@ -3549,13 +3549,13 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>75.71042910885556</v>
+        <v>73.83567729833796</v>
       </c>
       <c r="T38" t="n">
-        <v>172.4965164019307</v>
+        <v>172.4965164019308</v>
       </c>
       <c r="U38" t="n">
-        <v>234.3249969993996</v>
+        <v>236.1997488099172</v>
       </c>
       <c r="V38" t="n">
         <v>216.8510241668239</v>
@@ -3580,14 +3580,14 @@
         <v>0</v>
       </c>
       <c r="C39" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" t="n">
+        <v>149.980656540501</v>
+      </c>
+      <c r="E39" t="n">
         <v>337</v>
       </c>
-      <c r="D39" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" t="n">
-        <v>0</v>
-      </c>
       <c r="F39" t="n">
         <v>0</v>
       </c>
@@ -3595,7 +3595,7 @@
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>330.7762569977419</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -3631,10 +3631,10 @@
         <v>337</v>
       </c>
       <c r="T39" t="n">
-        <v>337</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>143.7569135382428</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
         <v>1.510667191520156</v>
@@ -3689,7 +3689,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>87.03776727492934</v>
+        <v>88.69257861566462</v>
       </c>
       <c r="N40" t="n">
         <v>139.6963703536521</v>
@@ -3704,7 +3704,7 @@
         <v>302.722266425598</v>
       </c>
       <c r="R40" t="n">
-        <v>308.1696361778723</v>
+        <v>306.5148248371369</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -3750,7 +3750,7 @@
         <v>91.88962870801186</v>
       </c>
       <c r="G41" t="n">
-        <v>90.48802555334787</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
         <v>92.25121146734651</v>
@@ -3786,10 +3786,10 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>175.7104291088556</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>110.8191366093336</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
@@ -3798,13 +3798,13 @@
         <v>316.8510241668239</v>
       </c>
       <c r="W41" t="n">
-        <v>250.958558705939</v>
+        <v>325.3734759809475</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>279.2818334606677</v>
       </c>
       <c r="Y41" t="n">
-        <v>198.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -3826,7 +3826,7 @@
         <v>29.67209722191262</v>
       </c>
       <c r="F42" t="n">
-        <v>26.63624233787687</v>
+        <v>123.862661066321</v>
       </c>
       <c r="G42" t="n">
         <v>12.59542266748017</v>
@@ -3859,7 +3859,7 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>97.22641872844413</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
         <v>225.3261369150208</v>
@@ -3929,22 +3929,22 @@
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>239.6963703536521</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>310.3682526036051</v>
+        <v>249.5616776741938</v>
       </c>
       <c r="P43" t="n">
         <v>337</v>
       </c>
       <c r="Q43" t="n">
-        <v>83.76497704274271</v>
+        <v>337</v>
       </c>
       <c r="R43" t="n">
         <v>337</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>47.26792232580625</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -3975,22 +3975,22 @@
         <v>174.9993129555745</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>142.4745782429939</v>
       </c>
       <c r="D44" t="n">
         <v>103.3391557398498</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>97.36328960686865</v>
       </c>
       <c r="F44" t="n">
         <v>97.88962870801186</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>96.48802555334787</v>
       </c>
       <c r="H44" t="n">
-        <v>98.25121146734651</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -4023,16 +4023,16 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>181.7104291088556</v>
       </c>
       <c r="T44" t="n">
-        <v>278.4965164019307</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>337</v>
+        <v>90.71415591767389</v>
       </c>
       <c r="V44" t="n">
-        <v>217.8537747272866</v>
+        <v>322.8510241668239</v>
       </c>
       <c r="W44" t="n">
         <v>0</v>
@@ -4096,10 +4096,10 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>7.226418728444286</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>231.3261369150208</v>
+        <v>238.552555643465</v>
       </c>
       <c r="S45" t="n">
         <v>156.8871603419698</v>
@@ -4160,28 +4160,28 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>98.58503799384475</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>194.6925786156646</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>245.6963703536521</v>
+        <v>175.1357521387545</v>
       </c>
       <c r="O46" t="n">
         <v>316.3682526036051</v>
       </c>
       <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
         <v>337</v>
       </c>
-      <c r="Q46" t="n">
-        <v>26.42968750139937</v>
-      </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>337</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>53.26792232580625</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
@@ -4321,25 +4321,25 @@
         <v>27.68</v>
       </c>
       <c r="J2" t="n">
-        <v>27.68</v>
+        <v>370.22</v>
       </c>
       <c r="K2" t="n">
-        <v>356.3800000000002</v>
+        <v>404.1392954271357</v>
       </c>
       <c r="L2" t="n">
-        <v>698.9200000000001</v>
+        <v>446.2191807537689</v>
       </c>
       <c r="M2" t="n">
-        <v>698.9200000000001</v>
+        <v>788.759180753769</v>
       </c>
       <c r="N2" t="n">
-        <v>698.9200000000001</v>
+        <v>788.759180753769</v>
       </c>
       <c r="O2" t="n">
-        <v>698.9200000000001</v>
+        <v>1131.299180753769</v>
       </c>
       <c r="P2" t="n">
-        <v>1041.46</v>
+        <v>1169.36006432857</v>
       </c>
       <c r="Q2" t="n">
         <v>1384</v>
@@ -4354,7 +4354,7 @@
         <v>1121.164701504256</v>
       </c>
       <c r="U2" t="n">
-        <v>901.0505184138018</v>
+        <v>876.518490585148</v>
       </c>
       <c r="V2" t="n">
         <v>675.9484738008483</v>
@@ -4376,28 +4376,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>241.9876701398865</v>
+        <v>641.9361743778742</v>
       </c>
       <c r="C3" t="n">
-        <v>241.9876701398865</v>
+        <v>576.105101450768</v>
       </c>
       <c r="D3" t="n">
-        <v>241.9876701398865</v>
+        <v>576.105101450768</v>
       </c>
       <c r="E3" t="n">
-        <v>241.9876701398865</v>
+        <v>576.105101450768</v>
       </c>
       <c r="F3" t="n">
-        <v>241.9876701398865</v>
+        <v>576.105101450768</v>
       </c>
       <c r="G3" t="n">
-        <v>241.9876701398865</v>
+        <v>576.105101450768</v>
       </c>
       <c r="H3" t="n">
-        <v>241.9876701398865</v>
+        <v>241.9876701399176</v>
       </c>
       <c r="I3" t="n">
-        <v>27.67999999996891</v>
+        <v>27.68</v>
       </c>
       <c r="J3" t="n">
         <v>164.0617971652541</v>
@@ -4424,28 +4424,28 @@
         <v>1227.754201452346</v>
       </c>
       <c r="R3" t="n">
-        <v>987.1862050355797</v>
+        <v>1095.10153790182</v>
       </c>
       <c r="S3" t="n">
-        <v>637.6912555406302</v>
+        <v>1037.639759778618</v>
       </c>
       <c r="T3" t="n">
-        <v>288.1963060456807</v>
+        <v>688.1448102836683</v>
       </c>
       <c r="U3" t="n">
-        <v>288.1963060456807</v>
+        <v>688.1448102836683</v>
       </c>
       <c r="V3" t="n">
-        <v>280.6097735289936</v>
+        <v>680.5582777669813</v>
       </c>
       <c r="W3" t="n">
-        <v>254.9803362463385</v>
+        <v>654.9288404843262</v>
       </c>
       <c r="X3" t="n">
-        <v>241.9876701398865</v>
+        <v>641.9361743778742</v>
       </c>
       <c r="Y3" t="n">
-        <v>241.9876701398865</v>
+        <v>641.9361743778742</v>
       </c>
     </row>
     <row r="4">
@@ -4455,40 +4455,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>314.8519809093739</v>
+        <v>807.2397405151413</v>
       </c>
       <c r="C4" t="n">
-        <v>314.8519809093739</v>
+        <v>940.1717463335771</v>
       </c>
       <c r="D4" t="n">
-        <v>314.8519809093739</v>
+        <v>1060.420890458577</v>
       </c>
       <c r="E4" t="n">
-        <v>439.6108851207869</v>
+        <v>1185.17979466999</v>
       </c>
       <c r="F4" t="n">
-        <v>570.9018577127224</v>
+        <v>1316.470767261926</v>
       </c>
       <c r="G4" t="n">
-        <v>731.3580350750175</v>
+        <v>1384</v>
       </c>
       <c r="H4" t="n">
-        <v>908.8680749885134</v>
+        <v>1384</v>
       </c>
       <c r="I4" t="n">
-        <v>908.8680749885134</v>
+        <v>1384</v>
       </c>
       <c r="J4" t="n">
-        <v>1251.408074988513</v>
+        <v>1384</v>
       </c>
       <c r="K4" t="n">
-        <v>1382.599187613906</v>
+        <v>1384</v>
       </c>
       <c r="L4" t="n">
         <v>1384</v>
       </c>
       <c r="M4" t="n">
-        <v>1291.106093661688</v>
+        <v>1288.350930691248</v>
       </c>
       <c r="N4" t="n">
         <v>1143.938042799413</v>
@@ -4509,22 +4509,22 @@
         <v>27.68</v>
       </c>
       <c r="T4" t="n">
-        <v>61.36426400879219</v>
+        <v>27.68</v>
       </c>
       <c r="U4" t="n">
-        <v>314.8519809093739</v>
+        <v>27.68</v>
       </c>
       <c r="V4" t="n">
-        <v>314.8519809093739</v>
+        <v>233.431392885946</v>
       </c>
       <c r="W4" t="n">
-        <v>314.8519809093739</v>
+        <v>412.2523111456234</v>
       </c>
       <c r="X4" t="n">
-        <v>314.8519809093739</v>
+        <v>570.2131021698169</v>
       </c>
       <c r="Y4" t="n">
-        <v>314.8519809093739</v>
+        <v>688.5524028488492</v>
       </c>
     </row>
     <row r="5">
@@ -4534,10 +4534,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>70.58361438686254</v>
+        <v>73.95649897256939</v>
       </c>
       <c r="C5" t="n">
-        <v>27.68</v>
+        <v>31.05288458570686</v>
       </c>
       <c r="D5" t="n">
         <v>27.68</v>
@@ -4567,7 +4567,7 @@
         <v>1055.3</v>
       </c>
       <c r="M5" t="n">
-        <v>1345.939116425199</v>
+        <v>1055.3</v>
       </c>
       <c r="N5" t="n">
         <v>1345.939116425199</v>
@@ -4588,22 +4588,22 @@
         <v>1301.464213021358</v>
       </c>
       <c r="T5" t="n">
-        <v>1121.164701504256</v>
+        <v>1145.69672933291</v>
       </c>
       <c r="U5" t="n">
-        <v>897.6776338280949</v>
+        <v>901.0505184138018</v>
       </c>
       <c r="V5" t="n">
-        <v>672.5755892151415</v>
+        <v>675.9484738008483</v>
       </c>
       <c r="W5" t="n">
-        <v>438.8650074162045</v>
+        <v>442.2378920019114</v>
       </c>
       <c r="X5" t="n">
-        <v>251.711640284217</v>
+        <v>255.0845248699238</v>
       </c>
       <c r="Y5" t="n">
-        <v>146.3404961601701</v>
+        <v>149.713380745877</v>
       </c>
     </row>
     <row r="6">
@@ -4613,10 +4613,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>798.1819729255566</v>
+        <v>716.8803429896864</v>
       </c>
       <c r="C6" t="n">
-        <v>798.1819729255566</v>
+        <v>716.8803429896864</v>
       </c>
       <c r="D6" t="n">
         <v>716.8803429896864</v>
@@ -4655,34 +4655,34 @@
         <v>1245.280652031104</v>
       </c>
       <c r="P6" t="n">
-        <v>1384.000000000028</v>
+        <v>1384.000000000017</v>
       </c>
       <c r="Q6" t="n">
-        <v>1384.000000000028</v>
+        <v>1384.000000000017</v>
       </c>
       <c r="R6" t="n">
-        <v>1251.347336449502</v>
+        <v>1251.347336449491</v>
       </c>
       <c r="S6" t="n">
-        <v>1193.8855583263</v>
+        <v>1193.885558326289</v>
       </c>
       <c r="T6" t="n">
-        <v>1193.8855583263</v>
+        <v>1112.58392839043</v>
       </c>
       <c r="U6" t="n">
-        <v>1193.8855583263</v>
+        <v>763.0889788954805</v>
       </c>
       <c r="V6" t="n">
-        <v>1186.299025809613</v>
+        <v>755.5024463787935</v>
       </c>
       <c r="W6" t="n">
-        <v>1160.669588526958</v>
+        <v>729.8730090961384</v>
       </c>
       <c r="X6" t="n">
-        <v>1147.676922420506</v>
+        <v>716.8803429896864</v>
       </c>
       <c r="Y6" t="n">
-        <v>798.1819729255566</v>
+        <v>716.8803429896864</v>
       </c>
     </row>
     <row r="7">
@@ -4692,19 +4692,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>73.94475689745182</v>
+        <v>499.6981128602461</v>
       </c>
       <c r="C7" t="n">
-        <v>73.94475689745182</v>
+        <v>499.6981128602461</v>
       </c>
       <c r="D7" t="n">
-        <v>83.19205869460247</v>
+        <v>499.6981128602461</v>
       </c>
       <c r="E7" t="n">
-        <v>207.9509629060155</v>
+        <v>499.6981128602461</v>
       </c>
       <c r="F7" t="n">
-        <v>339.241935497951</v>
+        <v>499.6981128602461</v>
       </c>
       <c r="G7" t="n">
         <v>499.6981128602461</v>
@@ -4725,10 +4725,10 @@
         <v>1384</v>
       </c>
       <c r="M7" t="n">
-        <v>1291.106093661688</v>
+        <v>1288.350930691248</v>
       </c>
       <c r="N7" t="n">
-        <v>1143.938042799413</v>
+        <v>1141.182879828973</v>
       </c>
       <c r="O7" t="n">
         <v>925.3842522907206</v>
@@ -4743,25 +4743,25 @@
         <v>27.68</v>
       </c>
       <c r="S7" t="n">
-        <v>73.94475689745182</v>
+        <v>27.68</v>
       </c>
       <c r="T7" t="n">
-        <v>73.94475689745182</v>
+        <v>40.45900307371835</v>
       </c>
       <c r="U7" t="n">
-        <v>73.94475689745182</v>
+        <v>293.9467199743001</v>
       </c>
       <c r="V7" t="n">
-        <v>73.94475689745182</v>
+        <v>499.6981128602461</v>
       </c>
       <c r="W7" t="n">
-        <v>73.94475689745182</v>
+        <v>499.6981128602461</v>
       </c>
       <c r="X7" t="n">
-        <v>73.94475689745182</v>
+        <v>499.6981128602461</v>
       </c>
       <c r="Y7" t="n">
-        <v>73.94475689745182</v>
+        <v>499.6981128602461</v>
       </c>
     </row>
     <row r="8">
@@ -4771,10 +4771,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>74.4364989725694</v>
+        <v>73.42447114391554</v>
       </c>
       <c r="C8" t="n">
-        <v>31.53288458570686</v>
+        <v>30.520856757053</v>
       </c>
       <c r="D8" t="n">
         <v>28.16</v>
@@ -4804,16 +4804,16 @@
         <v>725.12</v>
       </c>
       <c r="M8" t="n">
-        <v>725.12</v>
+        <v>1073.600000000007</v>
       </c>
       <c r="N8" t="n">
-        <v>1073.6</v>
+        <v>1369.939116425199</v>
       </c>
       <c r="O8" t="n">
-        <v>1073.6</v>
+        <v>1369.939116425199</v>
       </c>
       <c r="P8" t="n">
-        <v>1111.660883574801</v>
+        <v>1408</v>
       </c>
       <c r="Q8" t="n">
         <v>1408</v>
@@ -4822,25 +4822,25 @@
         <v>1408</v>
       </c>
       <c r="S8" t="n">
-        <v>1326.476240850012</v>
+        <v>1325.464213021358</v>
       </c>
       <c r="T8" t="n">
-        <v>1146.17672933291</v>
+        <v>1145.164701504256</v>
       </c>
       <c r="U8" t="n">
-        <v>901.5305184138018</v>
+        <v>900.518490585148</v>
       </c>
       <c r="V8" t="n">
-        <v>676.4284738008483</v>
+        <v>675.4164459721945</v>
       </c>
       <c r="W8" t="n">
-        <v>442.7178920019114</v>
+        <v>441.7058641732576</v>
       </c>
       <c r="X8" t="n">
-        <v>255.5645248699238</v>
+        <v>254.55249704127</v>
       </c>
       <c r="Y8" t="n">
-        <v>150.193380745877</v>
+        <v>149.1813529172231</v>
       </c>
     </row>
     <row r="9">
@@ -4850,76 +4850,76 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>248.4129944722148</v>
+        <v>816.1213668649153</v>
       </c>
       <c r="C9" t="n">
-        <v>248.4129944722148</v>
+        <v>748.2115351563284</v>
       </c>
       <c r="D9" t="n">
-        <v>248.4129944722148</v>
+        <v>396.75932616875</v>
       </c>
       <c r="E9" t="n">
-        <v>28.16</v>
+        <v>50.62589463146455</v>
       </c>
       <c r="F9" t="n">
-        <v>28.16</v>
+        <v>50.62589463146455</v>
       </c>
       <c r="G9" t="n">
-        <v>28.16</v>
+        <v>50.62589463146455</v>
       </c>
       <c r="H9" t="n">
-        <v>28.16</v>
+        <v>50.62589463146455</v>
       </c>
       <c r="I9" t="n">
-        <v>28.16</v>
+        <v>50.62589463146455</v>
       </c>
       <c r="J9" t="n">
-        <v>165.5959025337895</v>
+        <v>188.0617971652541</v>
       </c>
       <c r="K9" t="n">
-        <v>377.8271300432672</v>
+        <v>400.2930246747318</v>
       </c>
       <c r="L9" t="n">
-        <v>680.1555789026183</v>
+        <v>702.6214735340828</v>
       </c>
       <c r="M9" t="n">
-        <v>802.3859706454775</v>
+        <v>824.851865276942</v>
       </c>
       <c r="N9" t="n">
-        <v>972.77288421531</v>
+        <v>995.2387788467745</v>
       </c>
       <c r="O9" t="n">
-        <v>1245.760652031104</v>
+        <v>1268.226546662569</v>
       </c>
       <c r="P9" t="n">
-        <v>1385.534105368536</v>
+        <v>1408</v>
       </c>
       <c r="Q9" t="n">
-        <v>1385.534105368536</v>
+        <v>1408</v>
       </c>
       <c r="R9" t="n">
-        <v>1029.97854981298</v>
+        <v>1275.347336449474</v>
       </c>
       <c r="S9" t="n">
-        <v>972.5167716897781</v>
+        <v>1217.885558326272</v>
       </c>
       <c r="T9" t="n">
-        <v>972.5167716897781</v>
+        <v>1217.885558326272</v>
       </c>
       <c r="U9" t="n">
-        <v>972.5167716897781</v>
+        <v>862.3300027707095</v>
       </c>
       <c r="V9" t="n">
-        <v>616.9612161342225</v>
+        <v>854.7434702540224</v>
       </c>
       <c r="W9" t="n">
-        <v>261.4056605786669</v>
+        <v>829.1140329713674</v>
       </c>
       <c r="X9" t="n">
-        <v>248.4129944722148</v>
+        <v>816.1213668649153</v>
       </c>
       <c r="Y9" t="n">
-        <v>248.4129944722148</v>
+        <v>816.1213668649153</v>
       </c>
     </row>
     <row r="10">
@@ -4929,28 +4929,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>423.1474293695179</v>
+        <v>528.2231838040972</v>
       </c>
       <c r="C10" t="n">
-        <v>556.0794351879537</v>
+        <v>661.1551896225329</v>
       </c>
       <c r="D10" t="n">
-        <v>676.3285793129537</v>
+        <v>781.404333747533</v>
       </c>
       <c r="E10" t="n">
-        <v>801.0874835243667</v>
+        <v>906.163237958946</v>
       </c>
       <c r="F10" t="n">
-        <v>932.3784561163022</v>
+        <v>906.163237958946</v>
       </c>
       <c r="G10" t="n">
-        <v>932.3784561163022</v>
+        <v>906.163237958946</v>
       </c>
       <c r="H10" t="n">
-        <v>932.3784561163022</v>
+        <v>906.163237958946</v>
       </c>
       <c r="I10" t="n">
-        <v>932.3784561163022</v>
+        <v>906.163237958946</v>
       </c>
       <c r="J10" t="n">
         <v>1254.643237958953</v>
@@ -4986,19 +4986,19 @@
         <v>28.16</v>
       </c>
       <c r="U10" t="n">
-        <v>28.16</v>
+        <v>133.2357544345793</v>
       </c>
       <c r="V10" t="n">
-        <v>28.16</v>
+        <v>133.2357544345793</v>
       </c>
       <c r="W10" t="n">
-        <v>28.16</v>
+        <v>133.2357544345793</v>
       </c>
       <c r="X10" t="n">
-        <v>186.1207910241935</v>
+        <v>291.1965454587728</v>
       </c>
       <c r="Y10" t="n">
-        <v>304.4600917032258</v>
+        <v>409.535846137805</v>
       </c>
     </row>
     <row r="11">
@@ -5008,76 +5008,76 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>44.85881457825907</v>
+        <v>102.3727884953617</v>
       </c>
       <c r="C11" t="n">
-        <v>37.54751214211552</v>
+        <v>52.39846703779212</v>
       </c>
       <c r="D11" t="n">
-        <v>37.54751214211552</v>
+        <v>41.95487538137819</v>
       </c>
       <c r="E11" t="n">
-        <v>37.54751214211552</v>
+        <v>37.54751214211694</v>
       </c>
       <c r="F11" t="n">
-        <v>37.54751214211552</v>
+        <v>37.54751214211694</v>
       </c>
       <c r="G11" t="n">
-        <v>34.02425400742071</v>
+        <v>34.02425400742211</v>
       </c>
       <c r="H11" t="n">
-        <v>28.72</v>
+        <v>28.72000000000142</v>
       </c>
       <c r="I11" t="n">
-        <v>28.72</v>
+        <v>28.72000000000142</v>
       </c>
       <c r="J11" t="n">
-        <v>331.7091164251992</v>
+        <v>28.72000000000142</v>
       </c>
       <c r="K11" t="n">
-        <v>687.1191164251992</v>
+        <v>384.130000000019</v>
       </c>
       <c r="L11" t="n">
-        <v>1042.529116425199</v>
+        <v>739.5400000000366</v>
       </c>
       <c r="M11" t="n">
-        <v>1397.939116425199</v>
+        <v>739.5400000000366</v>
       </c>
       <c r="N11" t="n">
-        <v>1397.939116425199</v>
+        <v>1094.950000000053</v>
       </c>
       <c r="O11" t="n">
-        <v>1397.939116425199</v>
+        <v>1094.950000000053</v>
       </c>
       <c r="P11" t="n">
-        <v>1436</v>
+        <v>1436.000000000071</v>
       </c>
       <c r="Q11" t="n">
-        <v>1436</v>
+        <v>1436.000000000071</v>
       </c>
       <c r="R11" t="n">
-        <v>1436</v>
+        <v>1436.000000000071</v>
       </c>
       <c r="S11" t="n">
-        <v>1346.393505950651</v>
+        <v>1346.393505950722</v>
       </c>
       <c r="T11" t="n">
-        <v>1159.023287362842</v>
+        <v>1159.023287362913</v>
       </c>
       <c r="U11" t="n">
-        <v>907.3063693730269</v>
+        <v>907.3063693730976</v>
       </c>
       <c r="V11" t="n">
-        <v>675.1336176893664</v>
+        <v>675.1336176894371</v>
       </c>
       <c r="W11" t="n">
-        <v>434.3523288197223</v>
+        <v>434.3523288197931</v>
       </c>
       <c r="X11" t="n">
-        <v>240.1282546170277</v>
+        <v>240.1282546170984</v>
       </c>
       <c r="Y11" t="n">
-        <v>127.6864034222737</v>
+        <v>127.6864034223444</v>
       </c>
     </row>
     <row r="12">
@@ -5087,76 +5087,76 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>28.72</v>
+        <v>482.0528721252387</v>
       </c>
       <c r="C12" t="n">
-        <v>28.72</v>
+        <v>482.0528721252387</v>
       </c>
       <c r="D12" t="n">
-        <v>28.72</v>
+        <v>482.0528721252387</v>
       </c>
       <c r="E12" t="n">
-        <v>28.72</v>
+        <v>412.7433259423859</v>
       </c>
       <c r="F12" t="n">
-        <v>28.72</v>
+        <v>412.7433259423859</v>
       </c>
       <c r="G12" t="n">
-        <v>28.72</v>
+        <v>412.7433259423859</v>
       </c>
       <c r="H12" t="n">
-        <v>28.72</v>
+        <v>78.62589463153549</v>
       </c>
       <c r="I12" t="n">
-        <v>28.72</v>
+        <v>78.62589463153549</v>
       </c>
       <c r="J12" t="n">
-        <v>166.1559025337895</v>
+        <v>216.061797165325</v>
       </c>
       <c r="K12" t="n">
-        <v>378.3871300432672</v>
+        <v>428.2930246748027</v>
       </c>
       <c r="L12" t="n">
-        <v>680.7155789026183</v>
+        <v>730.6214735341538</v>
       </c>
       <c r="M12" t="n">
-        <v>802.9459706454775</v>
+        <v>852.851865277013</v>
       </c>
       <c r="N12" t="n">
-        <v>973.3328842153099</v>
+        <v>1023.238778846845</v>
       </c>
       <c r="O12" t="n">
-        <v>1246.320652031104</v>
+        <v>1296.22654666264</v>
       </c>
       <c r="P12" t="n">
-        <v>1386.094105368536</v>
+        <v>1436.000000000071</v>
       </c>
       <c r="Q12" t="n">
-        <v>1386.094105368536</v>
+        <v>1279.754201452417</v>
       </c>
       <c r="R12" t="n">
-        <v>1246.370734747302</v>
+        <v>917.1279388261366</v>
       </c>
       <c r="S12" t="n">
-        <v>1181.838249553393</v>
+        <v>554.5016761998556</v>
       </c>
       <c r="T12" t="n">
-        <v>819.2119869271307</v>
+        <v>549.676536948317</v>
       </c>
       <c r="U12" t="n">
-        <v>819.0090792219678</v>
+        <v>549.4736292431541</v>
       </c>
       <c r="V12" t="n">
-        <v>456.3828165957052</v>
+        <v>534.81638965576</v>
       </c>
       <c r="W12" t="n">
-        <v>423.682672242343</v>
+        <v>502.1162453023978</v>
       </c>
       <c r="X12" t="n">
-        <v>403.6192990651839</v>
+        <v>482.0528721252387</v>
       </c>
       <c r="Y12" t="n">
-        <v>391.3462626262626</v>
+        <v>482.0528721252387</v>
       </c>
     </row>
     <row r="13">
@@ -5166,76 +5166,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>600.6807243599757</v>
+        <v>651.6377563348243</v>
       </c>
       <c r="C13" t="n">
-        <v>600.6807243599757</v>
+        <v>651.6377563348243</v>
       </c>
       <c r="D13" t="n">
-        <v>713.9998684849758</v>
+        <v>764.9569004598244</v>
       </c>
       <c r="E13" t="n">
-        <v>831.8287726963888</v>
+        <v>764.9569004598244</v>
       </c>
       <c r="F13" t="n">
-        <v>956.1897452883243</v>
+        <v>889.3178730517599</v>
       </c>
       <c r="G13" t="n">
-        <v>956.1897452883243</v>
+        <v>889.3178730517599</v>
       </c>
       <c r="H13" t="n">
-        <v>956.1897452883243</v>
+        <v>956.1897452883095</v>
       </c>
       <c r="I13" t="n">
-        <v>956.1897452883243</v>
+        <v>956.1897452883095</v>
       </c>
       <c r="J13" t="n">
-        <v>1311.599745288324</v>
+        <v>1311.599745288326</v>
       </c>
       <c r="K13" t="n">
-        <v>1435.860857913717</v>
+        <v>1435.860857913719</v>
       </c>
       <c r="L13" t="n">
-        <v>1430.219405394682</v>
+        <v>1430.219405394684</v>
       </c>
       <c r="M13" t="n">
-        <v>1327.499629015223</v>
+        <v>1327.499629015224</v>
       </c>
       <c r="N13" t="n">
-        <v>1173.260871082241</v>
+        <v>1173.260871082242</v>
       </c>
       <c r="O13" t="n">
-        <v>947.6363735028419</v>
+        <v>947.6363735028433</v>
       </c>
       <c r="P13" t="n">
-        <v>672.0451541449196</v>
+        <v>672.0451541449211</v>
       </c>
       <c r="Q13" t="n">
-        <v>353.1337739170428</v>
+        <v>353.1337739170442</v>
       </c>
       <c r="R13" t="n">
-        <v>28.72</v>
+        <v>28.72000000000142</v>
       </c>
       <c r="S13" t="n">
-        <v>68.05475689745181</v>
+        <v>28.72000000000142</v>
       </c>
       <c r="T13" t="n">
-        <v>118.55911253532</v>
+        <v>217.306746371921</v>
       </c>
       <c r="U13" t="n">
-        <v>118.55911253532</v>
+        <v>217.306746371921</v>
       </c>
       <c r="V13" t="n">
-        <v>317.380505421266</v>
+        <v>217.306746371921</v>
       </c>
       <c r="W13" t="n">
-        <v>489.2714236809434</v>
+        <v>389.1976646315985</v>
       </c>
       <c r="X13" t="n">
-        <v>489.2714236809434</v>
+        <v>540.228455655792</v>
       </c>
       <c r="Y13" t="n">
-        <v>600.6807243599757</v>
+        <v>651.6377563348243</v>
       </c>
     </row>
     <row r="14">
@@ -5245,76 +5245,76 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>107.311807392342</v>
+        <v>107.3118073923434</v>
       </c>
       <c r="C14" t="n">
-        <v>57.33748593477237</v>
+        <v>57.3374859347738</v>
       </c>
       <c r="D14" t="n">
-        <v>46.89389427835845</v>
+        <v>46.89389427835987</v>
       </c>
       <c r="E14" t="n">
-        <v>42.48653103909719</v>
+        <v>42.48653103909862</v>
       </c>
       <c r="F14" t="n">
-        <v>37.54751214211552</v>
+        <v>37.54751214211694</v>
       </c>
       <c r="G14" t="n">
-        <v>34.02425400742069</v>
+        <v>34.02425400742213</v>
       </c>
       <c r="H14" t="n">
-        <v>28.72</v>
+        <v>28.72000000000142</v>
       </c>
       <c r="I14" t="n">
-        <v>28.72</v>
+        <v>28.72000000000142</v>
       </c>
       <c r="J14" t="n">
-        <v>289.6292310985659</v>
+        <v>28.72000000000142</v>
       </c>
       <c r="K14" t="n">
-        <v>645.0392310985659</v>
+        <v>384.130000000019</v>
       </c>
       <c r="L14" t="n">
-        <v>687.1191164251991</v>
+        <v>739.5400000000366</v>
       </c>
       <c r="M14" t="n">
-        <v>1042.529116425199</v>
+        <v>739.5400000000366</v>
       </c>
       <c r="N14" t="n">
-        <v>1397.939116425199</v>
+        <v>739.5400000000366</v>
       </c>
       <c r="O14" t="n">
-        <v>1397.939116425199</v>
+        <v>1080.590000000059</v>
       </c>
       <c r="P14" t="n">
-        <v>1436</v>
+        <v>1436.000000000069</v>
       </c>
       <c r="Q14" t="n">
-        <v>1436</v>
+        <v>1436.000000000069</v>
       </c>
       <c r="R14" t="n">
-        <v>1436</v>
+        <v>1436.000000000069</v>
       </c>
       <c r="S14" t="n">
-        <v>1346.393505950651</v>
+        <v>1346.39350595072</v>
       </c>
       <c r="T14" t="n">
-        <v>1159.023287362842</v>
+        <v>1159.023287362912</v>
       </c>
       <c r="U14" t="n">
-        <v>969.7593621871098</v>
+        <v>907.3063693730962</v>
       </c>
       <c r="V14" t="n">
-        <v>737.5866105034493</v>
+        <v>675.1336176894357</v>
       </c>
       <c r="W14" t="n">
-        <v>496.8053216338052</v>
+        <v>496.8053216338067</v>
       </c>
       <c r="X14" t="n">
-        <v>302.5812474311106</v>
+        <v>302.581247431112</v>
       </c>
       <c r="Y14" t="n">
-        <v>190.1393962363566</v>
+        <v>190.1393962363581</v>
       </c>
     </row>
     <row r="15">
@@ -5324,76 +5324,76 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>374.8534315372855</v>
+        <v>28.72000000000142</v>
       </c>
       <c r="C15" t="n">
-        <v>374.8534315372855</v>
+        <v>28.72000000000142</v>
       </c>
       <c r="D15" t="n">
-        <v>374.8534315372855</v>
+        <v>28.72000000000142</v>
       </c>
       <c r="E15" t="n">
-        <v>28.72</v>
+        <v>28.72000000000142</v>
       </c>
       <c r="F15" t="n">
-        <v>28.72</v>
+        <v>28.72000000000142</v>
       </c>
       <c r="G15" t="n">
-        <v>28.72</v>
+        <v>28.72000000000142</v>
       </c>
       <c r="H15" t="n">
-        <v>28.72</v>
+        <v>28.72000000000142</v>
       </c>
       <c r="I15" t="n">
-        <v>28.72</v>
+        <v>28.72000000000142</v>
       </c>
       <c r="J15" t="n">
-        <v>166.1559025337895</v>
+        <v>166.1559025337909</v>
       </c>
       <c r="K15" t="n">
-        <v>378.3871300432672</v>
+        <v>378.3871300432687</v>
       </c>
       <c r="L15" t="n">
-        <v>680.7155789026183</v>
+        <v>680.7155789026197</v>
       </c>
       <c r="M15" t="n">
-        <v>802.9459706454775</v>
+        <v>802.9459706454788</v>
       </c>
       <c r="N15" t="n">
-        <v>973.3328842153099</v>
+        <v>973.3328842153113</v>
       </c>
       <c r="O15" t="n">
-        <v>1246.320652031104</v>
+        <v>1246.320652031106</v>
       </c>
       <c r="P15" t="n">
-        <v>1386.094105368536</v>
+        <v>1386.094105368537</v>
       </c>
       <c r="Q15" t="n">
-        <v>1386.094105368536</v>
+        <v>1386.094105368537</v>
       </c>
       <c r="R15" t="n">
-        <v>1246.370734747302</v>
+        <v>1023.467842742262</v>
       </c>
       <c r="S15" t="n">
-        <v>1147.66624843573</v>
+        <v>811.561182034607</v>
       </c>
       <c r="T15" t="n">
-        <v>785.0399858094673</v>
+        <v>806.7360427830683</v>
       </c>
       <c r="U15" t="n">
-        <v>784.8370781043044</v>
+        <v>444.1097801567955</v>
       </c>
       <c r="V15" t="n">
-        <v>770.1798385169103</v>
+        <v>81.4835175305227</v>
       </c>
       <c r="W15" t="n">
-        <v>737.4796941635482</v>
+        <v>48.78337317716056</v>
       </c>
       <c r="X15" t="n">
-        <v>374.8534315372855</v>
+        <v>28.72000000000142</v>
       </c>
       <c r="Y15" t="n">
-        <v>374.8534315372855</v>
+        <v>28.72000000000142</v>
       </c>
     </row>
     <row r="16">
@@ -5403,76 +5403,76 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1044.654563834487</v>
+        <v>426.0217744770672</v>
       </c>
       <c r="C16" t="n">
-        <v>1044.654563834487</v>
+        <v>426.0217744770672</v>
       </c>
       <c r="D16" t="n">
-        <v>1157.973707959487</v>
+        <v>426.0217744770672</v>
       </c>
       <c r="E16" t="n">
-        <v>1157.973707959487</v>
+        <v>426.0217744770672</v>
       </c>
       <c r="F16" t="n">
-        <v>1282.334680551422</v>
+        <v>426.0217744770672</v>
       </c>
       <c r="G16" t="n">
-        <v>1435.860857913717</v>
+        <v>560.8797831600484</v>
       </c>
       <c r="H16" t="n">
-        <v>1435.860857913717</v>
+        <v>731.4598230735444</v>
       </c>
       <c r="I16" t="n">
-        <v>1435.860857913717</v>
+        <v>956.1897452883157</v>
       </c>
       <c r="J16" t="n">
-        <v>1435.860857913717</v>
+        <v>1311.599745288326</v>
       </c>
       <c r="K16" t="n">
-        <v>1435.860857913717</v>
+        <v>1435.860857913719</v>
       </c>
       <c r="L16" t="n">
-        <v>1430.219405394682</v>
+        <v>1430.219405394684</v>
       </c>
       <c r="M16" t="n">
-        <v>1327.499629015223</v>
+        <v>1327.499629015224</v>
       </c>
       <c r="N16" t="n">
-        <v>1173.260871082241</v>
+        <v>1173.260871082242</v>
       </c>
       <c r="O16" t="n">
-        <v>947.6363735028419</v>
+        <v>947.6363735028433</v>
       </c>
       <c r="P16" t="n">
-        <v>672.0451541449197</v>
+        <v>672.045154144921</v>
       </c>
       <c r="Q16" t="n">
-        <v>353.1337739170428</v>
+        <v>353.1337739170442</v>
       </c>
       <c r="R16" t="n">
-        <v>28.72</v>
+        <v>28.72000000000142</v>
       </c>
       <c r="S16" t="n">
-        <v>68.05475689745182</v>
+        <v>68.05475689745323</v>
       </c>
       <c r="T16" t="n">
-        <v>256.6415032693715</v>
+        <v>68.05475689745323</v>
       </c>
       <c r="U16" t="n">
-        <v>503.1992201699532</v>
+        <v>314.612473798035</v>
       </c>
       <c r="V16" t="n">
-        <v>702.020613055899</v>
+        <v>314.612473798035</v>
       </c>
       <c r="W16" t="n">
-        <v>821.4879254891622</v>
+        <v>314.612473798035</v>
       </c>
       <c r="X16" t="n">
-        <v>821.4879254891622</v>
+        <v>314.612473798035</v>
       </c>
       <c r="Y16" t="n">
-        <v>932.8972261681945</v>
+        <v>426.0217744770672</v>
       </c>
     </row>
     <row r="17">
@@ -5482,76 +5482,76 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>83.07967435343619</v>
+        <v>83.07967435343849</v>
       </c>
       <c r="C17" t="n">
-        <v>37.14575693627062</v>
+        <v>37.14575693627292</v>
       </c>
       <c r="D17" t="n">
-        <v>30.74256932026073</v>
+        <v>30.74256932026303</v>
       </c>
       <c r="E17" t="n">
-        <v>30.37561012140351</v>
+        <v>30.37561012140581</v>
       </c>
       <c r="F17" t="n">
-        <v>29.47699526482588</v>
+        <v>29.47699526482818</v>
       </c>
       <c r="G17" t="n">
-        <v>29.98384996701667</v>
+        <v>29.98384996701807</v>
       </c>
       <c r="H17" t="n">
-        <v>28.72</v>
+        <v>28.72000000000142</v>
       </c>
       <c r="I17" t="n">
-        <v>28.72</v>
+        <v>28.72000000000142</v>
       </c>
       <c r="J17" t="n">
-        <v>384.13</v>
+        <v>28.72000000000142</v>
       </c>
       <c r="K17" t="n">
-        <v>739.54</v>
+        <v>384.130000000019</v>
       </c>
       <c r="L17" t="n">
-        <v>1042.529116425199</v>
+        <v>739.5400000000366</v>
       </c>
       <c r="M17" t="n">
-        <v>1397.939116425199</v>
+        <v>1042.529116425259</v>
       </c>
       <c r="N17" t="n">
-        <v>1397.939116425199</v>
+        <v>1042.529116425259</v>
       </c>
       <c r="O17" t="n">
-        <v>1397.939116425199</v>
+        <v>1397.939116425269</v>
       </c>
       <c r="P17" t="n">
-        <v>1436</v>
+        <v>1436.000000000069</v>
       </c>
       <c r="Q17" t="n">
-        <v>1436</v>
+        <v>1436.000000000069</v>
       </c>
       <c r="R17" t="n">
-        <v>1436</v>
+        <v>1436.000000000069</v>
       </c>
       <c r="S17" t="n">
-        <v>1356.331537443</v>
+        <v>1350.433909991124</v>
       </c>
       <c r="T17" t="n">
-        <v>1173.001722895595</v>
+        <v>1167.104095443719</v>
       </c>
       <c r="U17" t="n">
-        <v>925.3252089461838</v>
+        <v>919.4275814943081</v>
       </c>
       <c r="V17" t="n">
-        <v>697.1928613029273</v>
+        <v>691.2952338510516</v>
       </c>
       <c r="W17" t="n">
-        <v>460.4519764736874</v>
+        <v>454.5543490218117</v>
       </c>
       <c r="X17" t="n">
-        <v>270.2683063113967</v>
+        <v>264.370678859521</v>
       </c>
       <c r="Y17" t="n">
-        <v>161.8668591570468</v>
+        <v>161.8668591570491</v>
       </c>
     </row>
     <row r="18">
@@ -5561,76 +5561,76 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1080.546605615949</v>
+        <v>1133.834777426365</v>
       </c>
       <c r="C18" t="n">
-        <v>717.9203429896863</v>
+        <v>1069.372551977266</v>
       </c>
       <c r="D18" t="n">
-        <v>717.9203429896863</v>
+        <v>717.9203429896879</v>
       </c>
       <c r="E18" t="n">
-        <v>371.7869114524009</v>
+        <v>371.7869114524024</v>
       </c>
       <c r="F18" t="n">
-        <v>28.72</v>
+        <v>28.72000000000142</v>
       </c>
       <c r="G18" t="n">
-        <v>28.72</v>
+        <v>28.72000000000142</v>
       </c>
       <c r="H18" t="n">
-        <v>28.72</v>
+        <v>28.72000000000142</v>
       </c>
       <c r="I18" t="n">
-        <v>28.72</v>
+        <v>28.72000000000142</v>
       </c>
       <c r="J18" t="n">
-        <v>166.1559025337895</v>
+        <v>166.1559025337909</v>
       </c>
       <c r="K18" t="n">
-        <v>378.3871300432672</v>
+        <v>378.3871300432687</v>
       </c>
       <c r="L18" t="n">
-        <v>680.7155789026183</v>
+        <v>680.7155789026197</v>
       </c>
       <c r="M18" t="n">
-        <v>802.9459706454775</v>
+        <v>802.9459706454788</v>
       </c>
       <c r="N18" t="n">
-        <v>973.3328842153099</v>
+        <v>973.3328842153113</v>
       </c>
       <c r="O18" t="n">
-        <v>1246.320652031104</v>
+        <v>1246.320652031106</v>
       </c>
       <c r="P18" t="n">
-        <v>1386.094105368536</v>
+        <v>1386.094105368537</v>
       </c>
       <c r="Q18" t="n">
-        <v>1386.094105368536</v>
+        <v>1386.094105368537</v>
       </c>
       <c r="R18" t="n">
-        <v>1250.411138787706</v>
+        <v>1250.411138787708</v>
       </c>
       <c r="S18" t="n">
-        <v>1189.919057634202</v>
+        <v>1189.919057634203</v>
       </c>
       <c r="T18" t="n">
-        <v>1189.134322423067</v>
+        <v>1189.134322423068</v>
       </c>
       <c r="U18" t="n">
-        <v>1189.134322423067</v>
+        <v>1189.134322423068</v>
       </c>
       <c r="V18" t="n">
-        <v>1125.229315065662</v>
+        <v>1178.517486876078</v>
       </c>
       <c r="W18" t="n">
-        <v>1096.569574752704</v>
+        <v>1149.85774656312</v>
       </c>
       <c r="X18" t="n">
-        <v>1080.546605615949</v>
+        <v>1133.834777426365</v>
       </c>
       <c r="Y18" t="n">
-        <v>1080.546605615949</v>
+        <v>1133.834777426365</v>
       </c>
     </row>
     <row r="19">
@@ -5640,76 +5640,76 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>985.9764868870609</v>
+        <v>1038.547975476042</v>
       </c>
       <c r="C19" t="n">
-        <v>1115.938492705497</v>
+        <v>1168.509981294477</v>
       </c>
       <c r="D19" t="n">
-        <v>1233.217636830497</v>
+        <v>1285.789125419478</v>
       </c>
       <c r="E19" t="n">
-        <v>1355.00654104191</v>
+        <v>1407.578029630891</v>
       </c>
       <c r="F19" t="n">
-        <v>1355.00654104191</v>
+        <v>1407.578029630891</v>
       </c>
       <c r="G19" t="n">
-        <v>1407.578029630889</v>
+        <v>1407.578029630891</v>
       </c>
       <c r="H19" t="n">
-        <v>1407.578029630889</v>
+        <v>1407.578029630891</v>
       </c>
       <c r="I19" t="n">
-        <v>1407.578029630889</v>
+        <v>1407.578029630891</v>
       </c>
       <c r="J19" t="n">
-        <v>1407.578029630889</v>
+        <v>1407.578029630891</v>
       </c>
       <c r="K19" t="n">
-        <v>1407.578029630889</v>
+        <v>1407.578029630891</v>
       </c>
       <c r="L19" t="n">
-        <v>1405.976981152258</v>
+        <v>1405.976981152259</v>
       </c>
       <c r="M19" t="n">
-        <v>1307.297608813203</v>
+        <v>1307.297608813204</v>
       </c>
       <c r="N19" t="n">
-        <v>1157.099254920625</v>
+        <v>1157.099254920626</v>
       </c>
       <c r="O19" t="n">
-        <v>935.5151613816297</v>
+        <v>935.5151613816313</v>
       </c>
       <c r="P19" t="n">
-        <v>663.9643460641115</v>
+        <v>663.964346064113</v>
       </c>
       <c r="Q19" t="n">
-        <v>349.0933698766388</v>
+        <v>349.0933698766402</v>
       </c>
       <c r="R19" t="n">
-        <v>28.72</v>
+        <v>28.72000000000142</v>
       </c>
       <c r="S19" t="n">
-        <v>28.72</v>
+        <v>28.72000000000142</v>
       </c>
       <c r="T19" t="n">
-        <v>221.2667463719196</v>
+        <v>221.266746371921</v>
       </c>
       <c r="U19" t="n">
-        <v>221.2667463719196</v>
+        <v>471.7844632725068</v>
       </c>
       <c r="V19" t="n">
-        <v>424.0481392578656</v>
+        <v>476.6196278468465</v>
       </c>
       <c r="W19" t="n">
-        <v>599.899057517543</v>
+        <v>652.4705461065239</v>
       </c>
       <c r="X19" t="n">
-        <v>754.8898485417366</v>
+        <v>807.4613371307174</v>
       </c>
       <c r="Y19" t="n">
-        <v>870.2591492207688</v>
+        <v>922.8306378097496</v>
       </c>
     </row>
     <row r="20">
@@ -5719,76 +5719,76 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>82.3226790886103</v>
+        <v>82.18105949686516</v>
       </c>
       <c r="C20" t="n">
-        <v>36.38876167144473</v>
+        <v>36.24714207969959</v>
       </c>
       <c r="D20" t="n">
-        <v>29.98557405543485</v>
+        <v>29.8439544636897</v>
       </c>
       <c r="E20" t="n">
-        <v>29.61861485657763</v>
+        <v>29.47699526483248</v>
       </c>
       <c r="F20" t="n">
-        <v>28.72</v>
+        <v>29.47699526483248</v>
       </c>
       <c r="G20" t="n">
-        <v>29.22685470218561</v>
+        <v>29.98384996701809</v>
       </c>
       <c r="H20" t="n">
-        <v>28.72</v>
+        <v>28.72000000000142</v>
       </c>
       <c r="I20" t="n">
-        <v>28.72</v>
+        <v>28.72000000000142</v>
       </c>
       <c r="J20" t="n">
-        <v>384.13</v>
+        <v>28.72000000000142</v>
       </c>
       <c r="K20" t="n">
-        <v>739.54</v>
+        <v>384.130000000019</v>
       </c>
       <c r="L20" t="n">
-        <v>1042.529116425199</v>
+        <v>687.1191164252485</v>
       </c>
       <c r="M20" t="n">
-        <v>1397.939116425199</v>
+        <v>687.1191164252485</v>
       </c>
       <c r="N20" t="n">
-        <v>1397.939116425199</v>
+        <v>1042.529116425259</v>
       </c>
       <c r="O20" t="n">
-        <v>1397.939116425199</v>
+        <v>1042.529116425259</v>
       </c>
       <c r="P20" t="n">
-        <v>1436</v>
+        <v>1080.590000000059</v>
       </c>
       <c r="Q20" t="n">
-        <v>1436</v>
+        <v>1436.000000000069</v>
       </c>
       <c r="R20" t="n">
-        <v>1436</v>
+        <v>1436.000000000069</v>
       </c>
       <c r="S20" t="n">
-        <v>1355.574542178174</v>
+        <v>1355.432922586429</v>
       </c>
       <c r="T20" t="n">
-        <v>1172.244727630769</v>
+        <v>1172.103108039024</v>
       </c>
       <c r="U20" t="n">
-        <v>924.568213681358</v>
+        <v>924.4265940896128</v>
       </c>
       <c r="V20" t="n">
-        <v>696.4358660381015</v>
+        <v>696.2942464463563</v>
       </c>
       <c r="W20" t="n">
-        <v>459.6949812088615</v>
+        <v>459.5533616171163</v>
       </c>
       <c r="X20" t="n">
-        <v>269.5113110465708</v>
+        <v>269.3696914548257</v>
       </c>
       <c r="Y20" t="n">
-        <v>161.1098638922209</v>
+        <v>160.9682443004758</v>
       </c>
     </row>
     <row r="21">
@@ -5798,76 +5798,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1080.546605615949</v>
+        <v>1133.834777426365</v>
       </c>
       <c r="C21" t="n">
-        <v>717.9203429896863</v>
+        <v>771.2085148000922</v>
       </c>
       <c r="D21" t="n">
-        <v>717.9203429896863</v>
+        <v>419.7563058125137</v>
       </c>
       <c r="E21" t="n">
-        <v>371.7869114524009</v>
+        <v>371.7869114524024</v>
       </c>
       <c r="F21" t="n">
-        <v>28.72</v>
+        <v>28.72000000000142</v>
       </c>
       <c r="G21" t="n">
-        <v>28.72</v>
+        <v>28.72000000000142</v>
       </c>
       <c r="H21" t="n">
-        <v>28.72</v>
+        <v>28.72000000000142</v>
       </c>
       <c r="I21" t="n">
-        <v>28.72</v>
+        <v>28.72000000000142</v>
       </c>
       <c r="J21" t="n">
-        <v>166.1559025337895</v>
+        <v>166.1559025337909</v>
       </c>
       <c r="K21" t="n">
-        <v>378.3871300432672</v>
+        <v>378.3871300432687</v>
       </c>
       <c r="L21" t="n">
-        <v>680.7155789026183</v>
+        <v>680.7155789026197</v>
       </c>
       <c r="M21" t="n">
-        <v>802.9459706454775</v>
+        <v>802.9459706454788</v>
       </c>
       <c r="N21" t="n">
-        <v>973.3328842153099</v>
+        <v>973.3328842153113</v>
       </c>
       <c r="O21" t="n">
-        <v>1246.320652031104</v>
+        <v>1246.320652031106</v>
       </c>
       <c r="P21" t="n">
-        <v>1386.094105368536</v>
+        <v>1386.094105368537</v>
       </c>
       <c r="Q21" t="n">
-        <v>1386.094105368536</v>
+        <v>1386.094105368537</v>
       </c>
       <c r="R21" t="n">
-        <v>1250.411138787706</v>
+        <v>1250.411138787708</v>
       </c>
       <c r="S21" t="n">
-        <v>1189.919057634202</v>
+        <v>1189.919057634203</v>
       </c>
       <c r="T21" t="n">
-        <v>1189.134322423067</v>
+        <v>1189.134322423068</v>
       </c>
       <c r="U21" t="n">
-        <v>1135.846150612652</v>
+        <v>1189.134322423068</v>
       </c>
       <c r="V21" t="n">
-        <v>1125.229315065662</v>
+        <v>1178.517486876078</v>
       </c>
       <c r="W21" t="n">
-        <v>1096.569574752704</v>
+        <v>1149.85774656312</v>
       </c>
       <c r="X21" t="n">
-        <v>1080.546605615949</v>
+        <v>1133.834777426365</v>
       </c>
       <c r="Y21" t="n">
-        <v>1080.546605615949</v>
+        <v>1133.834777426365</v>
       </c>
     </row>
     <row r="22">
@@ -5877,76 +5877,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>718.540917548391</v>
+        <v>850.4167744181261</v>
       </c>
       <c r="C22" t="n">
-        <v>718.540917548391</v>
+        <v>850.4167744181261</v>
       </c>
       <c r="D22" t="n">
-        <v>718.540917548391</v>
+        <v>850.4167744181261</v>
       </c>
       <c r="E22" t="n">
-        <v>718.540917548391</v>
+        <v>850.4167744181261</v>
       </c>
       <c r="F22" t="n">
-        <v>846.8618901403265</v>
+        <v>978.7377470100616</v>
       </c>
       <c r="G22" t="n">
-        <v>1004.348067502622</v>
+        <v>1136.223924372357</v>
       </c>
       <c r="H22" t="n">
-        <v>1178.888107416117</v>
+        <v>1310.763964285853</v>
       </c>
       <c r="I22" t="n">
-        <v>1407.578029630889</v>
+        <v>1407.57802963089</v>
       </c>
       <c r="J22" t="n">
-        <v>1407.578029630889</v>
+        <v>1407.57802963089</v>
       </c>
       <c r="K22" t="n">
-        <v>1407.578029630889</v>
+        <v>1407.57802963089</v>
       </c>
       <c r="L22" t="n">
-        <v>1405.976981152258</v>
+        <v>1405.976981152259</v>
       </c>
       <c r="M22" t="n">
-        <v>1307.297608813203</v>
+        <v>1307.297608813204</v>
       </c>
       <c r="N22" t="n">
-        <v>1157.099254920625</v>
+        <v>1157.099254920626</v>
       </c>
       <c r="O22" t="n">
-        <v>935.5151613816297</v>
+        <v>935.5151613816311</v>
       </c>
       <c r="P22" t="n">
-        <v>663.9643460641115</v>
+        <v>663.9643460641129</v>
       </c>
       <c r="Q22" t="n">
-        <v>349.0933698766388</v>
+        <v>349.0933698766402</v>
       </c>
       <c r="R22" t="n">
-        <v>28.72</v>
+        <v>28.72000000000142</v>
       </c>
       <c r="S22" t="n">
-        <v>28.72</v>
+        <v>28.72000000000142</v>
       </c>
       <c r="T22" t="n">
-        <v>221.2667463719196</v>
+        <v>221.266746371921</v>
       </c>
       <c r="U22" t="n">
-        <v>471.7844632725013</v>
+        <v>471.7844632725028</v>
       </c>
       <c r="V22" t="n">
-        <v>674.5658561584473</v>
+        <v>674.5658561584487</v>
       </c>
       <c r="W22" t="n">
-        <v>718.540917548391</v>
+        <v>850.4167744181261</v>
       </c>
       <c r="X22" t="n">
-        <v>718.540917548391</v>
+        <v>850.4167744181261</v>
       </c>
       <c r="Y22" t="n">
-        <v>718.540917548391</v>
+        <v>850.4167744181261</v>
       </c>
     </row>
     <row r="23">
@@ -5956,76 +5956,76 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>82.18105949685877</v>
+        <v>83.07967435344278</v>
       </c>
       <c r="C23" t="n">
-        <v>36.24714207969319</v>
+        <v>37.14575693627722</v>
       </c>
       <c r="D23" t="n">
-        <v>29.8439544636833</v>
+        <v>30.74256932026733</v>
       </c>
       <c r="E23" t="n">
-        <v>29.47699526482608</v>
+        <v>30.37561012141011</v>
       </c>
       <c r="F23" t="n">
-        <v>29.47699526482608</v>
+        <v>29.47699526483248</v>
       </c>
       <c r="G23" t="n">
-        <v>29.98384996701665</v>
+        <v>29.98384996701809</v>
       </c>
       <c r="H23" t="n">
-        <v>28.72</v>
+        <v>28.72000000000142</v>
       </c>
       <c r="I23" t="n">
-        <v>28.72</v>
+        <v>28.72000000000142</v>
       </c>
       <c r="J23" t="n">
-        <v>28.72</v>
+        <v>384.1300000000116</v>
       </c>
       <c r="K23" t="n">
-        <v>62.63929542713567</v>
+        <v>418.0492954271473</v>
       </c>
       <c r="L23" t="n">
-        <v>331.7091164251991</v>
+        <v>687.11911642525</v>
       </c>
       <c r="M23" t="n">
-        <v>687.1191164251991</v>
+        <v>1042.52911642526</v>
       </c>
       <c r="N23" t="n">
-        <v>1042.529116425199</v>
+        <v>1397.93911642527</v>
       </c>
       <c r="O23" t="n">
-        <v>1042.529116425199</v>
+        <v>1397.93911642527</v>
       </c>
       <c r="P23" t="n">
-        <v>1080.59</v>
+        <v>1436.000000000071</v>
       </c>
       <c r="Q23" t="n">
-        <v>1436</v>
+        <v>1436.000000000071</v>
       </c>
       <c r="R23" t="n">
-        <v>1436</v>
+        <v>1436.000000000071</v>
       </c>
       <c r="S23" t="n">
-        <v>1350.433909991055</v>
+        <v>1356.331537443006</v>
       </c>
       <c r="T23" t="n">
-        <v>1167.10409544365</v>
+        <v>1173.001722895602</v>
       </c>
       <c r="U23" t="n">
-        <v>924.4265940896064</v>
+        <v>925.3252089461904</v>
       </c>
       <c r="V23" t="n">
-        <v>696.2942464463499</v>
+        <v>697.1928613029339</v>
       </c>
       <c r="W23" t="n">
-        <v>459.5533616171099</v>
+        <v>460.4519764736939</v>
       </c>
       <c r="X23" t="n">
-        <v>269.3696914548193</v>
+        <v>270.2683063114033</v>
       </c>
       <c r="Y23" t="n">
-        <v>160.9682443004694</v>
+        <v>161.8668591570534</v>
       </c>
     </row>
     <row r="24">
@@ -6035,76 +6035,76 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>771.2085148001011</v>
+        <v>977.5889788787109</v>
       </c>
       <c r="C24" t="n">
-        <v>771.2085148001011</v>
+        <v>977.5889788787109</v>
       </c>
       <c r="D24" t="n">
-        <v>771.2085148001011</v>
+        <v>626.1367698911324</v>
       </c>
       <c r="E24" t="n">
-        <v>700.6711767730881</v>
+        <v>280.0033383538469</v>
       </c>
       <c r="F24" t="n">
-        <v>357.6042653206871</v>
+        <v>28.72000000000142</v>
       </c>
       <c r="G24" t="n">
-        <v>28.72</v>
+        <v>28.72000000000142</v>
       </c>
       <c r="H24" t="n">
-        <v>28.72</v>
+        <v>28.72000000000142</v>
       </c>
       <c r="I24" t="n">
-        <v>28.72</v>
+        <v>28.72000000000142</v>
       </c>
       <c r="J24" t="n">
-        <v>166.1559025337895</v>
+        <v>166.1559025337909</v>
       </c>
       <c r="K24" t="n">
-        <v>378.3871300432672</v>
+        <v>378.3871300432687</v>
       </c>
       <c r="L24" t="n">
-        <v>680.7155789026183</v>
+        <v>680.7155789026197</v>
       </c>
       <c r="M24" t="n">
-        <v>802.9459706454775</v>
+        <v>802.9459706454788</v>
       </c>
       <c r="N24" t="n">
-        <v>973.3328842153099</v>
+        <v>973.3328842153113</v>
       </c>
       <c r="O24" t="n">
-        <v>1246.320652031104</v>
+        <v>1246.320652031106</v>
       </c>
       <c r="P24" t="n">
-        <v>1386.094105368536</v>
+        <v>1386.094105368537</v>
       </c>
       <c r="Q24" t="n">
-        <v>1386.094105368536</v>
+        <v>1229.848306820883</v>
       </c>
       <c r="R24" t="n">
-        <v>1250.411138787706</v>
+        <v>1094.165340240054</v>
       </c>
       <c r="S24" t="n">
-        <v>1189.919057634202</v>
+        <v>1033.673259086549</v>
       </c>
       <c r="T24" t="n">
-        <v>1189.134322423067</v>
+        <v>1032.888523875414</v>
       </c>
       <c r="U24" t="n">
-        <v>1189.134322423067</v>
+        <v>1032.888523875414</v>
       </c>
       <c r="V24" t="n">
-        <v>1178.517486876077</v>
+        <v>1022.271688328424</v>
       </c>
       <c r="W24" t="n">
-        <v>1149.857746563119</v>
+        <v>993.6119480154661</v>
       </c>
       <c r="X24" t="n">
-        <v>1133.834777426364</v>
+        <v>977.5889788787109</v>
       </c>
       <c r="Y24" t="n">
-        <v>771.2085148001011</v>
+        <v>977.5889788787109</v>
       </c>
     </row>
     <row r="25">
@@ -6114,76 +6114,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>607.7938418039137</v>
+        <v>234.9098049229893</v>
       </c>
       <c r="C25" t="n">
-        <v>607.7938418039137</v>
+        <v>234.9098049229893</v>
       </c>
       <c r="D25" t="n">
-        <v>725.0729859289137</v>
+        <v>234.9098049229893</v>
       </c>
       <c r="E25" t="n">
-        <v>846.8618901403268</v>
+        <v>234.9098049229893</v>
       </c>
       <c r="F25" t="n">
-        <v>846.8618901403268</v>
+        <v>363.2307775149248</v>
       </c>
       <c r="G25" t="n">
-        <v>1004.348067502622</v>
+        <v>520.7169548772199</v>
       </c>
       <c r="H25" t="n">
-        <v>1178.888107416118</v>
+        <v>695.2569947907158</v>
       </c>
       <c r="I25" t="n">
-        <v>1407.578029630889</v>
+        <v>923.9469170054872</v>
       </c>
       <c r="J25" t="n">
-        <v>1407.578029630889</v>
+        <v>1279.356917005497</v>
       </c>
       <c r="K25" t="n">
-        <v>1407.578029630889</v>
+        <v>1407.57802963089</v>
       </c>
       <c r="L25" t="n">
-        <v>1405.976981152258</v>
+        <v>1405.976981152259</v>
       </c>
       <c r="M25" t="n">
-        <v>1307.297608813203</v>
+        <v>1307.297608813204</v>
       </c>
       <c r="N25" t="n">
-        <v>1157.099254920625</v>
+        <v>1157.099254920626</v>
       </c>
       <c r="O25" t="n">
-        <v>935.5151613816299</v>
+        <v>935.5151613816311</v>
       </c>
       <c r="P25" t="n">
-        <v>663.9643460641116</v>
+        <v>663.9643460641129</v>
       </c>
       <c r="Q25" t="n">
-        <v>349.0933698766388</v>
+        <v>349.0933698766402</v>
       </c>
       <c r="R25" t="n">
-        <v>28.72</v>
+        <v>28.72000000000142</v>
       </c>
       <c r="S25" t="n">
-        <v>28.72</v>
+        <v>72.01475689745322</v>
       </c>
       <c r="T25" t="n">
-        <v>28.72</v>
+        <v>72.01475689745322</v>
       </c>
       <c r="U25" t="n">
-        <v>279.2377169005817</v>
+        <v>79.91901389879578</v>
       </c>
       <c r="V25" t="n">
-        <v>452.8030507797201</v>
+        <v>79.91901389879578</v>
       </c>
       <c r="W25" t="n">
-        <v>452.8030507797201</v>
+        <v>79.91901389879578</v>
       </c>
       <c r="X25" t="n">
-        <v>607.7938418039137</v>
+        <v>234.9098049229893</v>
       </c>
       <c r="Y25" t="n">
-        <v>607.7938418039137</v>
+        <v>234.9098049229893</v>
       </c>
     </row>
     <row r="26">
@@ -6193,76 +6193,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>315.3302229830099</v>
+        <v>323.875010717584</v>
       </c>
       <c r="C26" t="n">
-        <v>220.9114570809959</v>
+        <v>229.4562448155699</v>
       </c>
       <c r="D26" t="n">
-        <v>166.0234209801375</v>
+        <v>174.5682087147115</v>
       </c>
       <c r="E26" t="n">
-        <v>117.1716132964318</v>
+        <v>125.7164010310058</v>
       </c>
       <c r="F26" t="n">
-        <v>67.78814995500569</v>
+        <v>125.7164010310058</v>
       </c>
       <c r="G26" t="n">
-        <v>67.78814995500569</v>
+        <v>77.74869845186655</v>
       </c>
       <c r="H26" t="n">
-        <v>28</v>
+        <v>28.00000000000142</v>
       </c>
       <c r="I26" t="n">
-        <v>28</v>
+        <v>28.00000000000142</v>
       </c>
       <c r="J26" t="n">
-        <v>28</v>
+        <v>374.5000000000164</v>
       </c>
       <c r="K26" t="n">
-        <v>374.5</v>
+        <v>408.4192954271521</v>
       </c>
       <c r="L26" t="n">
-        <v>707</v>
+        <v>668.9391164252402</v>
       </c>
       <c r="M26" t="n">
-        <v>707</v>
+        <v>1015.439116425255</v>
       </c>
       <c r="N26" t="n">
-        <v>707</v>
+        <v>1015.439116425255</v>
       </c>
       <c r="O26" t="n">
-        <v>707</v>
+        <v>1015.439116425255</v>
       </c>
       <c r="P26" t="n">
-        <v>1053.5</v>
+        <v>1053.500000000056</v>
       </c>
       <c r="Q26" t="n">
-        <v>1400</v>
+        <v>1400.000000000071</v>
       </c>
       <c r="R26" t="n">
-        <v>1400</v>
+        <v>1400.000000000071</v>
       </c>
       <c r="S26" t="n">
-        <v>1400</v>
+        <v>1309.151335882496</v>
       </c>
       <c r="T26" t="n">
-        <v>1400</v>
+        <v>1309.151335882496</v>
       </c>
       <c r="U26" t="n">
-        <v>1400</v>
+        <v>1012.989973448236</v>
       </c>
       <c r="V26" t="n">
-        <v>1123.382803871895</v>
+        <v>736.3727773201315</v>
       </c>
       <c r="W26" t="n">
-        <v>838.1570705578065</v>
+        <v>451.1470440060431</v>
       </c>
       <c r="X26" t="n">
-        <v>599.4885519106674</v>
+        <v>451.1470440060431</v>
       </c>
       <c r="Y26" t="n">
-        <v>442.6022562714691</v>
+        <v>451.1470440060431</v>
       </c>
     </row>
     <row r="27">
@@ -6272,76 +6272,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>310.957675624766</v>
+        <v>724.6022649877712</v>
       </c>
       <c r="C27" t="n">
-        <v>305.8062489121203</v>
+        <v>371.0669114524023</v>
       </c>
       <c r="D27" t="n">
-        <v>305.8062489121203</v>
+        <v>371.0669114524023</v>
       </c>
       <c r="E27" t="n">
-        <v>305.8062489121203</v>
+        <v>371.0669114524023</v>
       </c>
       <c r="F27" t="n">
-        <v>305.8062489121203</v>
+        <v>28.00000000000142</v>
       </c>
       <c r="G27" t="n">
-        <v>305.8062489121203</v>
+        <v>28.00000000000142</v>
       </c>
       <c r="H27" t="n">
-        <v>28</v>
+        <v>28.00000000000142</v>
       </c>
       <c r="I27" t="n">
-        <v>28</v>
+        <v>28.00000000000142</v>
       </c>
       <c r="J27" t="n">
-        <v>165.4359025337895</v>
+        <v>165.4359025337909</v>
       </c>
       <c r="K27" t="n">
-        <v>377.6671300432672</v>
+        <v>377.6671300432687</v>
       </c>
       <c r="L27" t="n">
-        <v>679.9955789026183</v>
+        <v>679.9955789026197</v>
       </c>
       <c r="M27" t="n">
-        <v>802.2259706454774</v>
+        <v>802.2259706454789</v>
       </c>
       <c r="N27" t="n">
-        <v>972.6128842153099</v>
+        <v>972.6128842153114</v>
       </c>
       <c r="O27" t="n">
-        <v>1245.600652031104</v>
+        <v>1245.600652031106</v>
       </c>
       <c r="P27" t="n">
-        <v>1385.374105368536</v>
+        <v>1385.374105368537</v>
       </c>
       <c r="Q27" t="n">
-        <v>1385.374105368536</v>
+        <v>1385.374105368537</v>
       </c>
       <c r="R27" t="n">
-        <v>1031.838751833182</v>
+        <v>1200.924917299187</v>
       </c>
       <c r="S27" t="n">
-        <v>678.3033982978284</v>
+        <v>1091.947987660834</v>
       </c>
       <c r="T27" t="n">
-        <v>629.0338146018453</v>
+        <v>1042.678403964851</v>
       </c>
       <c r="U27" t="n">
-        <v>584.3864624522379</v>
+        <v>998.0310518152431</v>
       </c>
       <c r="V27" t="n">
-        <v>525.2847784203993</v>
+        <v>938.9293677834046</v>
       </c>
       <c r="W27" t="n">
-        <v>448.1401896225927</v>
+        <v>861.784778985598</v>
       </c>
       <c r="X27" t="n">
-        <v>383.6323720009892</v>
+        <v>797.2769613639944</v>
       </c>
       <c r="Y27" t="n">
-        <v>339.8026823382272</v>
+        <v>753.4472717012324</v>
       </c>
     </row>
     <row r="28">
@@ -6351,76 +6351,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>795.6634127634491</v>
+        <v>774.8032855279666</v>
       </c>
       <c r="C28" t="n">
-        <v>878.1054185818848</v>
+        <v>857.2452913464024</v>
       </c>
       <c r="D28" t="n">
-        <v>947.8645627068848</v>
+        <v>927.0044354714024</v>
       </c>
       <c r="E28" t="n">
-        <v>1022.133466918298</v>
+        <v>1001.273339682816</v>
       </c>
       <c r="F28" t="n">
-        <v>1102.934439510233</v>
+        <v>1082.074312274751</v>
       </c>
       <c r="G28" t="n">
-        <v>1212.900616872529</v>
+        <v>1192.040489637046</v>
       </c>
       <c r="H28" t="n">
-        <v>1339.920656786025</v>
+        <v>1319.060529550542</v>
       </c>
       <c r="I28" t="n">
-        <v>1400</v>
+        <v>1319.060529550542</v>
       </c>
       <c r="J28" t="n">
-        <v>1400</v>
+        <v>1319.298887374678</v>
       </c>
       <c r="K28" t="n">
-        <v>1400</v>
+        <v>1400.000000000071</v>
       </c>
       <c r="L28" t="n">
-        <v>1349.91410303652</v>
+        <v>1400.000000000071</v>
       </c>
       <c r="M28" t="n">
-        <v>1202.749882212617</v>
+        <v>1400.000000000071</v>
       </c>
       <c r="N28" t="n">
-        <v>1004.06667983519</v>
+        <v>1329.486345549279</v>
       </c>
       <c r="O28" t="n">
-        <v>733.9977378113467</v>
+        <v>1059.417403525435</v>
       </c>
       <c r="P28" t="n">
-        <v>733.9977378113467</v>
+        <v>739.3817397230687</v>
       </c>
       <c r="Q28" t="n">
-        <v>380.4623842759931</v>
+        <v>385.8463861876998</v>
       </c>
       <c r="R28" t="n">
-        <v>32.31103265232954</v>
+        <v>32.31103265233096</v>
       </c>
       <c r="S28" t="n">
-        <v>28</v>
+        <v>28.00000000000142</v>
       </c>
       <c r="T28" t="n">
-        <v>173.0267463719196</v>
+        <v>173.026746371921</v>
       </c>
       <c r="U28" t="n">
-        <v>376.0244632725013</v>
+        <v>376.0244632725028</v>
       </c>
       <c r="V28" t="n">
-        <v>531.2858561584472</v>
+        <v>531.2858561584487</v>
       </c>
       <c r="W28" t="n">
-        <v>659.6167744181247</v>
+        <v>531.2858561584487</v>
       </c>
       <c r="X28" t="n">
-        <v>659.6167744181247</v>
+        <v>638.7566471826423</v>
       </c>
       <c r="Y28" t="n">
-        <v>727.4660750971569</v>
+        <v>706.6059478616745</v>
       </c>
     </row>
     <row r="29">
@@ -6430,76 +6430,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>76.82743004025231</v>
+        <v>71.32285728082148</v>
       </c>
       <c r="C29" t="n">
-        <v>76.82743004025231</v>
+        <v>71.32285728082148</v>
       </c>
       <c r="D29" t="n">
-        <v>28</v>
+        <v>71.32285728082148</v>
       </c>
       <c r="E29" t="n">
-        <v>28</v>
+        <v>71.32285728082148</v>
       </c>
       <c r="F29" t="n">
-        <v>28</v>
+        <v>28.00000000000142</v>
       </c>
       <c r="G29" t="n">
-        <v>28</v>
+        <v>28.00000000000142</v>
       </c>
       <c r="H29" t="n">
-        <v>28</v>
+        <v>28.00000000000142</v>
       </c>
       <c r="I29" t="n">
-        <v>28</v>
+        <v>28.00000000000142</v>
       </c>
       <c r="J29" t="n">
-        <v>28</v>
+        <v>374.5000000000165</v>
       </c>
       <c r="K29" t="n">
-        <v>374.5</v>
+        <v>408.4192954271522</v>
       </c>
       <c r="L29" t="n">
-        <v>721</v>
+        <v>450.4991807537854</v>
       </c>
       <c r="M29" t="n">
-        <v>721</v>
+        <v>796.9991807538006</v>
       </c>
       <c r="N29" t="n">
-        <v>1067.5</v>
+        <v>1143.499180753816</v>
       </c>
       <c r="O29" t="n">
-        <v>1067.5</v>
+        <v>1143.499180753816</v>
       </c>
       <c r="P29" t="n">
-        <v>1105.560883574801</v>
+        <v>1181.560064328617</v>
       </c>
       <c r="Q29" t="n">
-        <v>1400</v>
+        <v>1400.000000000071</v>
       </c>
       <c r="R29" t="n">
-        <v>1400</v>
+        <v>1400.000000000071</v>
       </c>
       <c r="S29" t="n">
-        <v>1272.009667566813</v>
+        <v>1400.000000000071</v>
       </c>
       <c r="T29" t="n">
-        <v>1046.255610595165</v>
+        <v>1400.000000000071</v>
       </c>
       <c r="U29" t="n">
-        <v>1009.982749526359</v>
+        <v>1109.899243626417</v>
       </c>
       <c r="V29" t="n">
-        <v>739.4261594588601</v>
+        <v>839.3426535589181</v>
       </c>
       <c r="W29" t="n">
-        <v>460.2610322053777</v>
+        <v>560.1775263054357</v>
       </c>
       <c r="X29" t="n">
-        <v>227.6531196188446</v>
+        <v>343.3599740872669</v>
       </c>
       <c r="Y29" t="n">
-        <v>76.82743004025231</v>
+        <v>192.5342845086745</v>
       </c>
     </row>
     <row r="30">
@@ -6509,76 +6509,76 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>242.3076701399175</v>
+        <v>779.429092536898</v>
       </c>
       <c r="C30" t="n">
-        <v>242.3076701399175</v>
+        <v>779.429092536898</v>
       </c>
       <c r="D30" t="n">
-        <v>242.3076701399175</v>
+        <v>779.429092536898</v>
       </c>
       <c r="E30" t="n">
-        <v>242.3076701399175</v>
+        <v>433.2956609996125</v>
       </c>
       <c r="F30" t="n">
-        <v>242.3076701399175</v>
+        <v>433.2956609996125</v>
       </c>
       <c r="G30" t="n">
-        <v>242.3076701399175</v>
+        <v>362.1174313108518</v>
       </c>
       <c r="H30" t="n">
-        <v>242.3076701399175</v>
+        <v>28.00000000000142</v>
       </c>
       <c r="I30" t="n">
-        <v>28</v>
+        <v>28.00000000000142</v>
       </c>
       <c r="J30" t="n">
-        <v>165.4359025337895</v>
+        <v>165.4359025337909</v>
       </c>
       <c r="K30" t="n">
-        <v>377.6671300432672</v>
+        <v>377.6671300432687</v>
       </c>
       <c r="L30" t="n">
-        <v>679.9955789026183</v>
+        <v>679.9955789026197</v>
       </c>
       <c r="M30" t="n">
-        <v>802.2259706454774</v>
+        <v>802.2259706454789</v>
       </c>
       <c r="N30" t="n">
-        <v>972.6128842153099</v>
+        <v>972.6128842153114</v>
       </c>
       <c r="O30" t="n">
-        <v>1245.600652031104</v>
+        <v>1245.600652031106</v>
       </c>
       <c r="P30" t="n">
-        <v>1385.374105368536</v>
+        <v>1385.374105368537</v>
       </c>
       <c r="Q30" t="n">
-        <v>1229.128306820881</v>
+        <v>1385.374105368537</v>
       </c>
       <c r="R30" t="n">
-        <v>1051.02109781581</v>
+        <v>1207.266896363465</v>
       </c>
       <c r="S30" t="n">
-        <v>948.1047742380625</v>
+        <v>1104.350572785718</v>
       </c>
       <c r="T30" t="n">
-        <v>904.8957966026856</v>
+        <v>1061.141595150341</v>
       </c>
       <c r="U30" t="n">
-        <v>866.3090505136843</v>
+        <v>1022.55484906134</v>
       </c>
       <c r="V30" t="n">
-        <v>763.1433015756249</v>
+        <v>969.5137710901072</v>
       </c>
       <c r="W30" t="n">
-        <v>692.0593188384245</v>
+        <v>898.4297883529066</v>
       </c>
       <c r="X30" t="n">
-        <v>633.612107277427</v>
+        <v>839.9825767919091</v>
       </c>
       <c r="Y30" t="n">
-        <v>595.8430236752711</v>
+        <v>802.2134931897532</v>
       </c>
     </row>
     <row r="31">
@@ -6588,76 +6588,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>301.0725617987263</v>
+        <v>634.7337269557671</v>
       </c>
       <c r="C31" t="n">
-        <v>389.4545676171621</v>
+        <v>634.7337269557671</v>
       </c>
       <c r="D31" t="n">
-        <v>465.1537117421622</v>
+        <v>710.4328710807672</v>
       </c>
       <c r="E31" t="n">
-        <v>545.3626159535752</v>
+        <v>790.6417752921802</v>
       </c>
       <c r="F31" t="n">
-        <v>632.1035885455107</v>
+        <v>877.3827478841157</v>
       </c>
       <c r="G31" t="n">
-        <v>748.0097659078058</v>
+        <v>993.2889252464108</v>
       </c>
       <c r="H31" t="n">
-        <v>880.9698058213017</v>
+        <v>1126.248965159907</v>
       </c>
       <c r="I31" t="n">
-        <v>1068.079728036073</v>
+        <v>1313.358887374678</v>
       </c>
       <c r="J31" t="n">
-        <v>1400</v>
+        <v>1313.358887374678</v>
       </c>
       <c r="K31" t="n">
-        <v>1400</v>
+        <v>1400.000000000071</v>
       </c>
       <c r="L31" t="n">
-        <v>1355.974709097127</v>
+        <v>1400.000000000071</v>
       </c>
       <c r="M31" t="n">
-        <v>1214.871094333829</v>
+        <v>1313.054100775737</v>
       </c>
       <c r="N31" t="n">
-        <v>1022.248498017009</v>
+        <v>1313.054100775737</v>
       </c>
       <c r="O31" t="n">
-        <v>758.2401620537711</v>
+        <v>1049.0457648125</v>
       </c>
       <c r="P31" t="n">
-        <v>444.2651043120105</v>
+        <v>735.0707070707394</v>
       </c>
       <c r="Q31" t="n">
-        <v>90.72975077665689</v>
+        <v>381.5353535353704</v>
       </c>
       <c r="R31" t="n">
-        <v>28</v>
+        <v>28.00000000000142</v>
       </c>
       <c r="S31" t="n">
-        <v>29.71475689745181</v>
+        <v>29.71475689745323</v>
       </c>
       <c r="T31" t="n">
-        <v>153.1459234534019</v>
+        <v>180.6815032693729</v>
       </c>
       <c r="U31" t="n">
-        <v>153.1459234534019</v>
+        <v>352.5361703507652</v>
       </c>
       <c r="V31" t="n">
-        <v>153.1459234534019</v>
+        <v>352.5361703507652</v>
       </c>
       <c r="W31" t="n">
-        <v>153.1459234534019</v>
+        <v>486.8070886104426</v>
       </c>
       <c r="X31" t="n">
-        <v>153.1459234534019</v>
+        <v>486.8070886104426</v>
       </c>
       <c r="Y31" t="n">
-        <v>226.9352241324341</v>
+        <v>560.5963892894749</v>
       </c>
     </row>
     <row r="32">
@@ -6667,76 +6667,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>67.73589291196333</v>
+        <v>67.73589291196475</v>
       </c>
       <c r="C32" t="n">
-        <v>27.86258155540382</v>
+        <v>27.86258155540525</v>
       </c>
       <c r="D32" t="n">
-        <v>27.52</v>
+        <v>27.52000000000142</v>
       </c>
       <c r="E32" t="n">
-        <v>27.52</v>
+        <v>27.52000000000142</v>
       </c>
       <c r="F32" t="n">
-        <v>27.52</v>
+        <v>27.52000000000142</v>
       </c>
       <c r="G32" t="n">
-        <v>27.52</v>
+        <v>27.52000000000142</v>
       </c>
       <c r="H32" t="n">
-        <v>27.52</v>
+        <v>27.52000000000142</v>
       </c>
       <c r="I32" t="n">
-        <v>27.52</v>
+        <v>27.52000000000142</v>
       </c>
       <c r="J32" t="n">
-        <v>27.52</v>
+        <v>368.0800000000158</v>
       </c>
       <c r="K32" t="n">
-        <v>61.43929542713568</v>
+        <v>708.6400000000334</v>
       </c>
       <c r="L32" t="n">
-        <v>103.5191807537689</v>
+        <v>1049.200000000051</v>
       </c>
       <c r="M32" t="n">
-        <v>103.5191807537689</v>
+        <v>1337.939116425312</v>
       </c>
       <c r="N32" t="n">
-        <v>354.3200000000001</v>
+        <v>1337.939116425312</v>
       </c>
       <c r="O32" t="n">
-        <v>694.8800000000001</v>
+        <v>1337.939116425312</v>
       </c>
       <c r="P32" t="n">
-        <v>1035.44</v>
+        <v>1376.000000000113</v>
       </c>
       <c r="Q32" t="n">
-        <v>1376</v>
+        <v>1376.000000000113</v>
       </c>
       <c r="R32" t="n">
-        <v>1376</v>
+        <v>1376.000000000071</v>
       </c>
       <c r="S32" t="n">
-        <v>1296.494516051661</v>
+        <v>1296.494516051732</v>
       </c>
       <c r="T32" t="n">
-        <v>1119.225307564862</v>
+        <v>1119.225307564933</v>
       </c>
       <c r="U32" t="n">
-        <v>877.609399676057</v>
+        <v>879.6783972016822</v>
       </c>
       <c r="V32" t="n">
-        <v>655.5376580934067</v>
+        <v>657.6066556190317</v>
       </c>
       <c r="W32" t="n">
-        <v>426.9263768503963</v>
+        <v>426.9263768503977</v>
       </c>
       <c r="X32" t="n">
-        <v>242.8033127487117</v>
+        <v>242.8033127487132</v>
       </c>
       <c r="Y32" t="n">
-        <v>140.4624716549679</v>
+        <v>140.4624716549693</v>
       </c>
     </row>
     <row r="33">
@@ -6746,76 +6746,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>361.6374313108504</v>
+        <v>370.5869114524023</v>
       </c>
       <c r="C33" t="n">
-        <v>361.6374313108504</v>
+        <v>370.5869114524023</v>
       </c>
       <c r="D33" t="n">
-        <v>361.6374313108504</v>
+        <v>370.5869114524023</v>
       </c>
       <c r="E33" t="n">
-        <v>361.6374313108504</v>
+        <v>370.5869114524023</v>
       </c>
       <c r="F33" t="n">
-        <v>361.6374313108504</v>
+        <v>27.52000000000142</v>
       </c>
       <c r="G33" t="n">
-        <v>361.6374313108504</v>
+        <v>27.52000000000142</v>
       </c>
       <c r="H33" t="n">
-        <v>27.52</v>
+        <v>27.52000000000142</v>
       </c>
       <c r="I33" t="n">
-        <v>27.52</v>
+        <v>27.52000000000142</v>
       </c>
       <c r="J33" t="n">
-        <v>164.9559025337895</v>
+        <v>156.0617971653671</v>
       </c>
       <c r="K33" t="n">
-        <v>377.1871300432672</v>
+        <v>368.2930246748448</v>
       </c>
       <c r="L33" t="n">
-        <v>679.5155789026182</v>
+        <v>670.6214735341958</v>
       </c>
       <c r="M33" t="n">
-        <v>792.851865276942</v>
+        <v>792.851865277055</v>
       </c>
       <c r="N33" t="n">
-        <v>963.2387788467745</v>
+        <v>963.2387788468875</v>
       </c>
       <c r="O33" t="n">
-        <v>1236.226546662569</v>
+        <v>1236.226546662682</v>
       </c>
       <c r="P33" t="n">
-        <v>1376</v>
+        <v>1376.000000000113</v>
       </c>
       <c r="Q33" t="n">
-        <v>1376</v>
+        <v>1376.000000000113</v>
       </c>
       <c r="R33" t="n">
-        <v>1246.377639479777</v>
+        <v>1102.654133216812</v>
       </c>
       <c r="S33" t="n">
-        <v>1191.946164386878</v>
+        <v>755.1793857420496</v>
       </c>
       <c r="T33" t="n">
-        <v>1191.946164386878</v>
+        <v>407.7046382672874</v>
       </c>
       <c r="U33" t="n">
-        <v>1191.946164386878</v>
+        <v>407.7046382672874</v>
       </c>
       <c r="V33" t="n">
-        <v>1187.389934900494</v>
+        <v>403.1484087809034</v>
       </c>
       <c r="W33" t="n">
-        <v>1164.790800648142</v>
+        <v>380.5492745285513</v>
       </c>
       <c r="X33" t="n">
-        <v>1056.586926260346</v>
+        <v>370.5869114524023</v>
       </c>
       <c r="Y33" t="n">
-        <v>709.112178785598</v>
+        <v>370.5869114524023</v>
       </c>
     </row>
     <row r="34">
@@ -6825,76 +6825,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>994.6341120844169</v>
+        <v>287.9350857843951</v>
       </c>
       <c r="C34" t="n">
-        <v>994.6341120844169</v>
+        <v>287.9350857843951</v>
       </c>
       <c r="D34" t="n">
-        <v>1117.853256209417</v>
+        <v>411.1542299093952</v>
       </c>
       <c r="E34" t="n">
-        <v>1245.58216042083</v>
+        <v>411.1542299093952</v>
       </c>
       <c r="F34" t="n">
-        <v>1368.413344788622</v>
+        <v>545.4152025013307</v>
       </c>
       <c r="G34" t="n">
-        <v>1368.413344788622</v>
+        <v>708.8413798636258</v>
       </c>
       <c r="H34" t="n">
-        <v>1368.413344788622</v>
+        <v>889.3214197771217</v>
       </c>
       <c r="I34" t="n">
-        <v>1368.413344788622</v>
+        <v>889.3214197771217</v>
       </c>
       <c r="J34" t="n">
-        <v>1368.413344788622</v>
+        <v>1229.881419777136</v>
       </c>
       <c r="K34" t="n">
-        <v>1368.413344788622</v>
+        <v>1364.042532402529</v>
       </c>
       <c r="L34" t="n">
-        <v>1368.413344788622</v>
+        <v>1368.413344788623</v>
       </c>
       <c r="M34" t="n">
-        <v>1275.794578510172</v>
+        <v>1275.794578510174</v>
       </c>
       <c r="N34" t="n">
-        <v>1131.656830678201</v>
+        <v>1131.656830678202</v>
       </c>
       <c r="O34" t="n">
-        <v>916.1333431998115</v>
+        <v>916.1333431998129</v>
       </c>
       <c r="P34" t="n">
-        <v>650.6431339428993</v>
+        <v>650.6431339429007</v>
       </c>
       <c r="Q34" t="n">
-        <v>341.8327638160327</v>
+        <v>341.8327638160341</v>
       </c>
       <c r="R34" t="n">
-        <v>27.52</v>
+        <v>27.52000000000142</v>
       </c>
       <c r="S34" t="n">
-        <v>27.52</v>
+        <v>27.52000000000142</v>
       </c>
       <c r="T34" t="n">
-        <v>226.0067463719196</v>
+        <v>27.52000000000142</v>
       </c>
       <c r="U34" t="n">
-        <v>482.4644632725013</v>
+        <v>44.96844743907077</v>
       </c>
       <c r="V34" t="n">
-        <v>691.1858561584473</v>
+        <v>44.96844743907077</v>
       </c>
       <c r="W34" t="n">
-        <v>872.9767744181247</v>
+        <v>44.96844743907077</v>
       </c>
       <c r="X34" t="n">
-        <v>872.9767744181247</v>
+        <v>44.96844743907077</v>
       </c>
       <c r="Y34" t="n">
-        <v>872.9767744181247</v>
+        <v>166.277748118103</v>
       </c>
     </row>
     <row r="35">
@@ -6931,10 +6931,10 @@
         <v>360.59</v>
       </c>
       <c r="K35" t="n">
-        <v>694.2199999999999</v>
+        <v>600.5992310985661</v>
       </c>
       <c r="L35" t="n">
-        <v>976.3091164251992</v>
+        <v>642.6791164251993</v>
       </c>
       <c r="M35" t="n">
         <v>976.3091164251992</v>
@@ -6955,22 +6955,22 @@
         <v>1348</v>
       </c>
       <c r="S35" t="n">
-        <v>1273.418507779456</v>
+        <v>1271.524819081964</v>
       </c>
       <c r="T35" t="n">
-        <v>1099.179602322961</v>
+        <v>1097.285913625468</v>
       </c>
       <c r="U35" t="n">
-        <v>860.5939974644587</v>
+        <v>858.7003087669661</v>
       </c>
       <c r="V35" t="n">
-        <v>641.5525589121113</v>
+        <v>639.6588702146188</v>
       </c>
       <c r="W35" t="n">
-        <v>413.9025831737804</v>
+        <v>412.0088944762879</v>
       </c>
       <c r="X35" t="n">
-        <v>232.8098221023988</v>
+        <v>230.9161334049063</v>
       </c>
       <c r="Y35" t="n">
         <v>133.499284038958</v>
@@ -6983,19 +6983,19 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>247.359889001307</v>
+        <v>910.555975864645</v>
       </c>
       <c r="C36" t="n">
-        <v>247.359889001307</v>
+        <v>910.555975864645</v>
       </c>
       <c r="D36" t="n">
-        <v>247.359889001307</v>
+        <v>910.555975864645</v>
       </c>
       <c r="E36" t="n">
-        <v>247.359889001307</v>
+        <v>570.1519354606046</v>
       </c>
       <c r="F36" t="n">
-        <v>241.2676701399176</v>
+        <v>570.1519354606046</v>
       </c>
       <c r="G36" t="n">
         <v>241.2676701399176</v>
@@ -7031,28 +7031,28 @@
         <v>1348</v>
       </c>
       <c r="R36" t="n">
-        <v>1007.59595959596</v>
+        <v>1221.40794251008</v>
       </c>
       <c r="S36" t="n">
-        <v>956.1947875333639</v>
+        <v>938.5827935886209</v>
       </c>
       <c r="T36" t="n">
-        <v>615.7907471293234</v>
+        <v>938.5827935886209</v>
       </c>
       <c r="U36" t="n">
-        <v>275.386706725283</v>
+        <v>938.5827935886209</v>
       </c>
       <c r="V36" t="n">
-        <v>273.8607802692021</v>
+        <v>937.05686713254</v>
       </c>
       <c r="W36" t="n">
-        <v>254.2919490471531</v>
+        <v>917.488035910491</v>
       </c>
       <c r="X36" t="n">
-        <v>247.359889001307</v>
+        <v>910.555975864645</v>
       </c>
       <c r="Y36" t="n">
-        <v>247.359889001307</v>
+        <v>910.555975864645</v>
       </c>
     </row>
     <row r="37">
@@ -7062,43 +7062,43 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>836.2197405151412</v>
+        <v>714.7099919277441</v>
       </c>
       <c r="C37" t="n">
-        <v>975.091746333577</v>
+        <v>853.5819977461799</v>
       </c>
       <c r="D37" t="n">
-        <v>1101.280890458577</v>
+        <v>853.5819977461799</v>
       </c>
       <c r="E37" t="n">
-        <v>1203.528074988663</v>
+        <v>853.5819977461799</v>
       </c>
       <c r="F37" t="n">
-        <v>1203.528074988663</v>
+        <v>990.8129703381154</v>
       </c>
       <c r="G37" t="n">
-        <v>1203.528074988663</v>
+        <v>1157.209147700411</v>
       </c>
       <c r="H37" t="n">
-        <v>1203.528074988663</v>
+        <v>1340.659187613906</v>
       </c>
       <c r="I37" t="n">
-        <v>1203.528074988663</v>
+        <v>1340.659187613906</v>
       </c>
       <c r="J37" t="n">
-        <v>1203.528074988663</v>
+        <v>1340.659187613906</v>
       </c>
       <c r="K37" t="n">
-        <v>1340.659187614056</v>
+        <v>1340.659187613906</v>
       </c>
       <c r="L37" t="n">
-        <v>1348.000000000149</v>
+        <v>1348</v>
       </c>
       <c r="M37" t="n">
-        <v>1260.083063358657</v>
+        <v>1258.411536751854</v>
       </c>
       <c r="N37" t="n">
-        <v>1118.975618556988</v>
+        <v>1117.304091950185</v>
       </c>
       <c r="O37" t="n">
         <v>906.4824341089025</v>
@@ -7113,25 +7113,25 @@
         <v>26.96</v>
       </c>
       <c r="S37" t="n">
-        <v>26.96</v>
+        <v>79.16475689745181</v>
       </c>
       <c r="T37" t="n">
-        <v>26.96</v>
+        <v>280.6215032693714</v>
       </c>
       <c r="U37" t="n">
-        <v>26.96</v>
+        <v>301.9025625582262</v>
       </c>
       <c r="V37" t="n">
-        <v>238.651392885946</v>
+        <v>301.9025625582262</v>
       </c>
       <c r="W37" t="n">
-        <v>423.4123111456233</v>
+        <v>301.9025625582262</v>
       </c>
       <c r="X37" t="n">
-        <v>587.3131021698168</v>
+        <v>465.8033535824198</v>
       </c>
       <c r="Y37" t="n">
-        <v>711.5924028488491</v>
+        <v>590.082654261452</v>
       </c>
     </row>
     <row r="38">
@@ -7165,25 +7165,25 @@
         <v>26.96</v>
       </c>
       <c r="J38" t="n">
-        <v>26.96</v>
+        <v>360.59</v>
       </c>
       <c r="K38" t="n">
-        <v>360.59</v>
+        <v>394.5092954271356</v>
       </c>
       <c r="L38" t="n">
-        <v>694.2199999999999</v>
+        <v>642.6791164251993</v>
       </c>
       <c r="M38" t="n">
+        <v>976.3091164251992</v>
+      </c>
+      <c r="N38" t="n">
+        <v>976.3091164251992</v>
+      </c>
+      <c r="O38" t="n">
+        <v>976.3091164251992</v>
+      </c>
+      <c r="P38" t="n">
         <v>1014.37</v>
-      </c>
-      <c r="N38" t="n">
-        <v>1014.37</v>
-      </c>
-      <c r="O38" t="n">
-        <v>1014.37</v>
-      </c>
-      <c r="P38" t="n">
-        <v>1348</v>
       </c>
       <c r="Q38" t="n">
         <v>1348</v>
@@ -7192,10 +7192,10 @@
         <v>1348</v>
       </c>
       <c r="S38" t="n">
-        <v>1271.524819081964</v>
+        <v>1273.418507779457</v>
       </c>
       <c r="T38" t="n">
-        <v>1097.285913625468</v>
+        <v>1099.179602322961</v>
       </c>
       <c r="U38" t="n">
         <v>860.5939974644587</v>
@@ -7220,22 +7220,22 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>367.3640404040404</v>
+        <v>852.9770843820636</v>
       </c>
       <c r="C39" t="n">
-        <v>26.96</v>
+        <v>852.9770843820636</v>
       </c>
       <c r="D39" t="n">
-        <v>26.96</v>
+        <v>701.4814717148909</v>
       </c>
       <c r="E39" t="n">
-        <v>26.96</v>
+        <v>361.0774313108504</v>
       </c>
       <c r="F39" t="n">
-        <v>26.96</v>
+        <v>361.0774313108504</v>
       </c>
       <c r="G39" t="n">
-        <v>26.96</v>
+        <v>361.0774313108504</v>
       </c>
       <c r="H39" t="n">
         <v>26.96</v>
@@ -7250,16 +7250,16 @@
         <v>376.6271300432672</v>
       </c>
       <c r="L39" t="n">
-        <v>642.6214735340828</v>
+        <v>678.9555789026183</v>
       </c>
       <c r="M39" t="n">
-        <v>764.851865276942</v>
+        <v>801.1859706454775</v>
       </c>
       <c r="N39" t="n">
-        <v>935.2387788467745</v>
+        <v>971.57288421531</v>
       </c>
       <c r="O39" t="n">
-        <v>1208.226546662569</v>
+        <v>1244.560652031104</v>
       </c>
       <c r="P39" t="n">
         <v>1348</v>
@@ -7274,22 +7274,22 @@
         <v>881.0039021060395</v>
       </c>
       <c r="T39" t="n">
-        <v>540.5998617019991</v>
+        <v>881.0039021060395</v>
       </c>
       <c r="U39" t="n">
-        <v>395.3908581280164</v>
+        <v>881.0039021060395</v>
       </c>
       <c r="V39" t="n">
-        <v>393.8649316719354</v>
+        <v>879.4779756499586</v>
       </c>
       <c r="W39" t="n">
-        <v>374.2961004498864</v>
+        <v>859.9091444279096</v>
       </c>
       <c r="X39" t="n">
-        <v>367.3640404040404</v>
+        <v>852.9770843820636</v>
       </c>
       <c r="Y39" t="n">
-        <v>367.3640404040404</v>
+        <v>852.9770843820636</v>
       </c>
     </row>
     <row r="40">
@@ -7299,76 +7299,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>552.1057668603551</v>
+        <v>211.7209182596774</v>
       </c>
       <c r="C40" t="n">
-        <v>552.1057668603551</v>
+        <v>350.5929240781132</v>
       </c>
       <c r="D40" t="n">
-        <v>552.1057668603551</v>
+        <v>350.5929240781132</v>
       </c>
       <c r="E40" t="n">
-        <v>552.1057668603551</v>
+        <v>350.5929240781132</v>
       </c>
       <c r="F40" t="n">
-        <v>552.1057668603551</v>
+        <v>487.8238966700487</v>
       </c>
       <c r="G40" t="n">
-        <v>552.1057668603551</v>
+        <v>639.6389651598356</v>
       </c>
       <c r="H40" t="n">
-        <v>632.298152773742</v>
+        <v>639.6389651598356</v>
       </c>
       <c r="I40" t="n">
-        <v>869.8980749885135</v>
+        <v>877.2388873746071</v>
       </c>
       <c r="J40" t="n">
-        <v>1203.528074988513</v>
+        <v>1210.868887374607</v>
       </c>
       <c r="K40" t="n">
-        <v>1340.659187613906</v>
+        <v>1348</v>
       </c>
       <c r="L40" t="n">
         <v>1348</v>
       </c>
       <c r="M40" t="n">
-        <v>1260.083063358657</v>
+        <v>1258.411536751854</v>
       </c>
       <c r="N40" t="n">
-        <v>1118.975618556988</v>
+        <v>1117.304091950185</v>
       </c>
       <c r="O40" t="n">
-        <v>906.4824341089025</v>
+        <v>904.810907502099</v>
       </c>
       <c r="P40" t="n">
-        <v>644.0225278822933</v>
+        <v>642.3510012754898</v>
       </c>
       <c r="Q40" t="n">
-        <v>338.2424607857296</v>
+        <v>336.5709341789261</v>
       </c>
       <c r="R40" t="n">
         <v>26.96</v>
       </c>
       <c r="S40" t="n">
-        <v>79.16475689745181</v>
+        <v>26.96</v>
       </c>
       <c r="T40" t="n">
-        <v>79.16475689745181</v>
+        <v>26.96</v>
       </c>
       <c r="U40" t="n">
-        <v>79.16475689745181</v>
+        <v>26.96</v>
       </c>
       <c r="V40" t="n">
-        <v>79.16475689745181</v>
+        <v>26.96</v>
       </c>
       <c r="W40" t="n">
-        <v>263.9256751571292</v>
+        <v>211.7209182596774</v>
       </c>
       <c r="X40" t="n">
-        <v>427.8264661813228</v>
+        <v>211.7209182596774</v>
       </c>
       <c r="Y40" t="n">
-        <v>552.1057668603551</v>
+        <v>211.7209182596774</v>
       </c>
     </row>
     <row r="41">
@@ -7378,19 +7378,19 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>396.64904579351</v>
+        <v>305.2469997800273</v>
       </c>
       <c r="C41" t="n">
-        <v>396.64904579351</v>
+        <v>305.2469997800273</v>
       </c>
       <c r="D41" t="n">
-        <v>396.64904579351</v>
+        <v>305.2469997800273</v>
       </c>
       <c r="E41" t="n">
-        <v>304.3628946754609</v>
+        <v>212.9608486619782</v>
       </c>
       <c r="F41" t="n">
-        <v>211.5450878996913</v>
+        <v>120.1430418862086</v>
       </c>
       <c r="G41" t="n">
         <v>120.1430418862086</v>
@@ -7402,25 +7402,25 @@
         <v>26.96</v>
       </c>
       <c r="J41" t="n">
-        <v>26.96</v>
+        <v>360.59</v>
       </c>
       <c r="K41" t="n">
-        <v>360.59</v>
+        <v>694.2199999999999</v>
       </c>
       <c r="L41" t="n">
-        <v>694.2199999999999</v>
+        <v>976.3091164251992</v>
       </c>
       <c r="M41" t="n">
         <v>976.3091164251992</v>
       </c>
       <c r="N41" t="n">
-        <v>1309.939116425199</v>
+        <v>976.3091164251992</v>
       </c>
       <c r="O41" t="n">
-        <v>1309.939116425199</v>
+        <v>976.3091164251992</v>
       </c>
       <c r="P41" t="n">
-        <v>1348</v>
+        <v>1014.37</v>
       </c>
       <c r="Q41" t="n">
         <v>1348</v>
@@ -7429,25 +7429,25 @@
         <v>1348</v>
       </c>
       <c r="S41" t="n">
-        <v>1170.514718071863</v>
+        <v>1348</v>
       </c>
       <c r="T41" t="n">
-        <v>1170.514718071863</v>
+        <v>1236.06147817239</v>
       </c>
       <c r="U41" t="n">
-        <v>1170.514718071863</v>
+        <v>1236.06147817239</v>
       </c>
       <c r="V41" t="n">
-        <v>850.4631785094145</v>
+        <v>916.0099386099419</v>
       </c>
       <c r="W41" t="n">
-        <v>596.9696848670519</v>
+        <v>587.3498618615099</v>
       </c>
       <c r="X41" t="n">
-        <v>596.9696848670519</v>
+        <v>305.2469997800273</v>
       </c>
       <c r="Y41" t="n">
-        <v>396.64904579351</v>
+        <v>305.2469997800273</v>
       </c>
     </row>
     <row r="42">
@@ -7457,16 +7457,16 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>198.3919379477106</v>
+        <v>296.6004417138158</v>
       </c>
       <c r="C42" t="n">
-        <v>149.8061678007214</v>
+        <v>248.0146715668266</v>
       </c>
       <c r="D42" t="n">
-        <v>114.5155749747592</v>
+        <v>212.7240787408643</v>
       </c>
       <c r="E42" t="n">
-        <v>84.54375959908984</v>
+        <v>182.752263365195</v>
       </c>
       <c r="F42" t="n">
         <v>57.63846430830512</v>
@@ -7502,31 +7502,31 @@
         <v>1348</v>
       </c>
       <c r="Q42" t="n">
-        <v>1249.791496233895</v>
+        <v>1348</v>
       </c>
       <c r="R42" t="n">
-        <v>1022.189337733874</v>
+        <v>1120.397841499979</v>
       </c>
       <c r="S42" t="n">
-        <v>869.778064661177</v>
+        <v>967.9865684272822</v>
       </c>
       <c r="T42" t="n">
-        <v>777.0741375308505</v>
+        <v>875.2826412969557</v>
       </c>
       <c r="U42" t="n">
-        <v>688.9924419468997</v>
+        <v>787.2009457130049</v>
       </c>
       <c r="V42" t="n">
-        <v>586.4564144807177</v>
+        <v>684.6649182468229</v>
       </c>
       <c r="W42" t="n">
-        <v>465.8774822485677</v>
+        <v>564.0859860146729</v>
       </c>
       <c r="X42" t="n">
-        <v>357.9353211926207</v>
+        <v>456.1438249587259</v>
       </c>
       <c r="Y42" t="n">
-        <v>270.6712880955153</v>
+        <v>368.8797918616204</v>
       </c>
     </row>
     <row r="43">
@@ -7542,16 +7542,16 @@
         <v>643.9762096060784</v>
       </c>
       <c r="D43" t="n">
-        <v>666.0825991167693</v>
+        <v>671.1653537310785</v>
       </c>
       <c r="E43" t="n">
-        <v>697.7815033281823</v>
+        <v>702.8642579424916</v>
       </c>
       <c r="F43" t="n">
-        <v>736.0124759201178</v>
+        <v>741.0952305344271</v>
       </c>
       <c r="G43" t="n">
-        <v>803.408653282413</v>
+        <v>808.4914078967222</v>
       </c>
       <c r="H43" t="n">
         <v>887.8586931959089</v>
@@ -7572,19 +7572,19 @@
         <v>1348</v>
       </c>
       <c r="N43" t="n">
-        <v>1105.88245418823</v>
+        <v>1348</v>
       </c>
       <c r="O43" t="n">
-        <v>792.3791687300431</v>
+        <v>1095.917497298794</v>
       </c>
       <c r="P43" t="n">
-        <v>451.9751283260027</v>
+        <v>755.5134568947537</v>
       </c>
       <c r="Q43" t="n">
-        <v>367.3640404040404</v>
+        <v>415.1094164907134</v>
       </c>
       <c r="R43" t="n">
-        <v>26.96</v>
+        <v>74.70537608667298</v>
       </c>
       <c r="S43" t="n">
         <v>26.96</v>
@@ -7615,22 +7615,22 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>329.4650463789982</v>
+        <v>569.944523081891</v>
       </c>
       <c r="C44" t="n">
-        <v>329.4650463789982</v>
+        <v>426.0308076849275</v>
       </c>
       <c r="D44" t="n">
-        <v>225.0820607831903</v>
+        <v>321.6478220891196</v>
       </c>
       <c r="E44" t="n">
-        <v>225.0820607831903</v>
+        <v>223.3010649104644</v>
       </c>
       <c r="F44" t="n">
-        <v>126.2036479468147</v>
+        <v>124.4226520740888</v>
       </c>
       <c r="G44" t="n">
-        <v>126.2036479468147</v>
+        <v>26.96</v>
       </c>
       <c r="H44" t="n">
         <v>26.96</v>
@@ -7642,22 +7642,22 @@
         <v>360.59</v>
       </c>
       <c r="K44" t="n">
-        <v>694.2199999999999</v>
+        <v>394.5092954271356</v>
       </c>
       <c r="L44" t="n">
+        <v>436.5891807537688</v>
+      </c>
+      <c r="M44" t="n">
+        <v>770.2191807537688</v>
+      </c>
+      <c r="N44" t="n">
         <v>976.3091164251992</v>
       </c>
-      <c r="M44" t="n">
+      <c r="O44" t="n">
         <v>976.3091164251992</v>
       </c>
-      <c r="N44" t="n">
-        <v>1309.939116425199</v>
-      </c>
-      <c r="O44" t="n">
-        <v>1309.939116425199</v>
-      </c>
       <c r="P44" t="n">
-        <v>1348</v>
+        <v>1014.37</v>
       </c>
       <c r="Q44" t="n">
         <v>1348</v>
@@ -7666,25 +7666,25 @@
         <v>1348</v>
       </c>
       <c r="S44" t="n">
-        <v>1348</v>
+        <v>1164.454112011257</v>
       </c>
       <c r="T44" t="n">
-        <v>1066.690387472797</v>
+        <v>1164.454112011257</v>
       </c>
       <c r="U44" t="n">
-        <v>726.2863470687569</v>
+        <v>1072.823651488354</v>
       </c>
       <c r="V44" t="n">
-        <v>506.2320291624068</v>
+        <v>746.7115058652996</v>
       </c>
       <c r="W44" t="n">
-        <v>506.2320291624068</v>
+        <v>746.7115058652996</v>
       </c>
       <c r="X44" t="n">
-        <v>506.2320291624068</v>
+        <v>746.7115058652996</v>
       </c>
       <c r="Y44" t="n">
-        <v>506.2320291624068</v>
+        <v>746.7115058652996</v>
       </c>
     </row>
     <row r="45">
@@ -7718,10 +7718,10 @@
         <v>26.96</v>
       </c>
       <c r="J45" t="n">
-        <v>128.0617971652541</v>
+        <v>164.3959025337895</v>
       </c>
       <c r="K45" t="n">
-        <v>340.2930246747318</v>
+        <v>376.6271300432672</v>
       </c>
       <c r="L45" t="n">
         <v>642.6214735340828</v>
@@ -7739,7 +7739,7 @@
         <v>1348</v>
       </c>
       <c r="Q45" t="n">
-        <v>1340.700587142986</v>
+        <v>1348</v>
       </c>
       <c r="R45" t="n">
         <v>1107.037822582359</v>
@@ -7803,25 +7803,25 @@
         <v>1258.042754614309</v>
       </c>
       <c r="L46" t="n">
-        <v>1158.46190815588</v>
+        <v>1258.042754614309</v>
       </c>
       <c r="M46" t="n">
-        <v>961.8027378370269</v>
+        <v>1258.042754614309</v>
       </c>
       <c r="N46" t="n">
-        <v>713.624585964651</v>
+        <v>1081.137954474153</v>
       </c>
       <c r="O46" t="n">
-        <v>394.060694445858</v>
+        <v>761.5740629553599</v>
       </c>
       <c r="P46" t="n">
-        <v>53.65665404181755</v>
+        <v>761.5740629553599</v>
       </c>
       <c r="Q46" t="n">
-        <v>26.96</v>
+        <v>421.1700225513194</v>
       </c>
       <c r="R46" t="n">
-        <v>26.96</v>
+        <v>80.76598214727905</v>
       </c>
       <c r="S46" t="n">
         <v>26.96</v>
@@ -7964,28 +7964,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>12.18253890840691</v>
+        <v>358.1825389084069</v>
       </c>
       <c r="K2" t="n">
-        <v>297.7582874473379</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>303.4950653266332</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>496.9671979940761</v>
+        <v>842.9671979940761</v>
       </c>
       <c r="N2" t="n">
         <v>429.1887470145588</v>
       </c>
       <c r="O2" t="n">
-        <v>24.86597510173064</v>
+        <v>370.8659751017306</v>
       </c>
       <c r="P2" t="n">
-        <v>307.5546630557568</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>489.7362672420583</v>
+        <v>360.5442830717859</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8043,7 +8043,7 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J3" t="n">
-        <v>226.3999890303093</v>
+        <v>226.3999890302779</v>
       </c>
       <c r="K3" t="n">
         <v>295.8802408630135</v>
@@ -8210,10 +8210,10 @@
         <v>303.4950653266332</v>
       </c>
       <c r="M5" t="n">
-        <v>790.5420630700347</v>
+        <v>496.9671979940761</v>
       </c>
       <c r="N5" t="n">
-        <v>429.1887470145588</v>
+        <v>722.7636120905175</v>
       </c>
       <c r="O5" t="n">
         <v>24.86597510173064</v>
@@ -8298,7 +8298,7 @@
         <v>382.6817988009037</v>
       </c>
       <c r="P6" t="n">
-        <v>218.0859589430672</v>
+        <v>218.0859589430557</v>
       </c>
       <c r="Q6" t="n">
         <v>17.27519534353338</v>
@@ -8447,10 +8447,10 @@
         <v>309.4950653266332</v>
       </c>
       <c r="M8" t="n">
-        <v>496.9671979940761</v>
+        <v>848.967197994083</v>
       </c>
       <c r="N8" t="n">
-        <v>781.1887470145589</v>
+        <v>728.5211878480867</v>
       </c>
       <c r="O8" t="n">
         <v>24.86597510173064</v>
@@ -8459,7 +8459,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>443.068708075593</v>
+        <v>143.7362672420583</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8675,25 +8675,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J11" t="n">
-        <v>318.2321514591132</v>
+        <v>12.18253890840691</v>
       </c>
       <c r="K11" t="n">
-        <v>324.7380854271357</v>
+        <v>324.7380854271534</v>
       </c>
       <c r="L11" t="n">
-        <v>316.4950653266332</v>
+        <v>316.4950653266509</v>
       </c>
       <c r="M11" t="n">
-        <v>855.9671979940761</v>
+        <v>496.9671979940761</v>
       </c>
       <c r="N11" t="n">
-        <v>429.1887470145588</v>
+        <v>788.1887470145753</v>
       </c>
       <c r="O11" t="n">
         <v>24.86597510173064</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>306.0496125507246</v>
       </c>
       <c r="Q11" t="n">
         <v>143.7362672420583</v>
@@ -8912,25 +8912,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J14" t="n">
-        <v>275.7272167857462</v>
+        <v>12.18253890840691</v>
       </c>
       <c r="K14" t="n">
-        <v>324.7380854271357</v>
+        <v>324.7380854271534</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>316.4950653266509</v>
       </c>
       <c r="M14" t="n">
-        <v>855.9671979940761</v>
+        <v>496.9671979940761</v>
       </c>
       <c r="N14" t="n">
-        <v>788.1887470145589</v>
+        <v>429.1887470145588</v>
       </c>
       <c r="O14" t="n">
-        <v>24.86597510173064</v>
+        <v>369.3609245967031</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>320.5546630557669</v>
       </c>
       <c r="Q14" t="n">
         <v>143.7362672420583</v>
@@ -9149,22 +9149,22 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>371.1825389084069</v>
+        <v>12.18253890840691</v>
       </c>
       <c r="K17" t="n">
-        <v>324.7380854271357</v>
+        <v>324.7380854271534</v>
       </c>
       <c r="L17" t="n">
-        <v>263.5446778773394</v>
+        <v>316.4950653266509</v>
       </c>
       <c r="M17" t="n">
-        <v>855.9671979940761</v>
+        <v>803.0168105448053</v>
       </c>
       <c r="N17" t="n">
         <v>429.1887470145588</v>
       </c>
       <c r="O17" t="n">
-        <v>24.86597510173064</v>
+        <v>383.8659751017407</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -9386,19 +9386,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>371.1825389084069</v>
+        <v>12.18253890840691</v>
       </c>
       <c r="K20" t="n">
-        <v>324.7380854271357</v>
+        <v>324.7380854271534</v>
       </c>
       <c r="L20" t="n">
-        <v>263.5446778773394</v>
+        <v>263.5446778773701</v>
       </c>
       <c r="M20" t="n">
-        <v>855.9671979940761</v>
+        <v>496.9671979940761</v>
       </c>
       <c r="N20" t="n">
-        <v>429.1887470145588</v>
+        <v>788.1887470145689</v>
       </c>
       <c r="O20" t="n">
         <v>24.86597510173064</v>
@@ -9407,7 +9407,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>143.7362672420583</v>
+        <v>502.7362672420684</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9623,19 +9623,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J23" t="n">
-        <v>12.18253890840691</v>
+        <v>371.1825389084171</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>229.282763304475</v>
+        <v>229.2827633045147</v>
       </c>
       <c r="M23" t="n">
-        <v>855.9671979940761</v>
+        <v>855.9671979940863</v>
       </c>
       <c r="N23" t="n">
-        <v>788.1887470145589</v>
+        <v>788.1887470145691</v>
       </c>
       <c r="O23" t="n">
         <v>24.86597510173064</v>
@@ -9644,7 +9644,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>502.7362672420583</v>
+        <v>143.7362672420583</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -9860,16 +9860,16 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J26" t="n">
-        <v>12.18253890840691</v>
+        <v>362.1825389084221</v>
       </c>
       <c r="K26" t="n">
-        <v>315.7380854271357</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>293.3536511852191</v>
+        <v>220.6463996681363</v>
       </c>
       <c r="M26" t="n">
-        <v>496.9671979940761</v>
+        <v>846.9671979940912</v>
       </c>
       <c r="N26" t="n">
         <v>429.1887470145588</v>
@@ -9878,10 +9878,10 @@
         <v>24.86597510173064</v>
       </c>
       <c r="P26" t="n">
-        <v>311.5546630557568</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>493.7362672420583</v>
+        <v>493.7362672420735</v>
       </c>
       <c r="R26" t="n">
         <v>294.54111633436</v>
@@ -10097,19 +10097,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J29" t="n">
-        <v>12.18253890840691</v>
+        <v>362.1825389084222</v>
       </c>
       <c r="K29" t="n">
-        <v>315.7380854271357</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>307.4950653266332</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>496.9671979940761</v>
+        <v>846.9671979940914</v>
       </c>
       <c r="N29" t="n">
-        <v>779.1887470145589</v>
+        <v>779.1887470145741</v>
       </c>
       <c r="O29" t="n">
         <v>24.86597510173064</v>
@@ -10118,7 +10118,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>441.149516156401</v>
+        <v>364.382666910194</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10334,28 +10334,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J32" t="n">
-        <v>12.18253890840691</v>
+        <v>356.1825389084215</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>309.7380854271534</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>301.4950653266509</v>
       </c>
       <c r="M32" t="n">
-        <v>496.9671979940761</v>
+        <v>788.6228711509057</v>
       </c>
       <c r="N32" t="n">
-        <v>682.5229078693378</v>
+        <v>429.1887470145588</v>
       </c>
       <c r="O32" t="n">
-        <v>368.8659751017306</v>
+        <v>24.86597510173064</v>
       </c>
       <c r="P32" t="n">
-        <v>305.5546630557568</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>487.7362672420583</v>
+        <v>143.7362672420583</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10413,7 +10413,7 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J33" t="n">
-        <v>227.4647419277884</v>
+        <v>218.4807971111987</v>
       </c>
       <c r="K33" t="n">
         <v>295.8802408630135</v>
@@ -10422,7 +10422,7 @@
         <v>388.0893364597981</v>
       </c>
       <c r="M33" t="n">
-        <v>462.7108756134049</v>
+        <v>471.6948204301074</v>
       </c>
       <c r="N33" t="n">
         <v>485.4085271713503</v>
@@ -10574,13 +10574,13 @@
         <v>349.1825389084069</v>
       </c>
       <c r="K35" t="n">
-        <v>302.7380854271357</v>
+        <v>208.1716521933641</v>
       </c>
       <c r="L35" t="n">
-        <v>242.4335667662284</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>496.9671979940761</v>
+        <v>833.9671979940761</v>
       </c>
       <c r="N35" t="n">
         <v>429.1887470145588</v>
@@ -10808,16 +10808,16 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J38" t="n">
-        <v>12.18253890840691</v>
+        <v>349.1825389084069</v>
       </c>
       <c r="K38" t="n">
-        <v>302.7380854271357</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>294.4950653266332</v>
+        <v>208.1716521933641</v>
       </c>
       <c r="M38" t="n">
-        <v>820.3510363779145</v>
+        <v>833.9671979940761</v>
       </c>
       <c r="N38" t="n">
         <v>429.1887470145588</v>
@@ -10826,10 +10826,10 @@
         <v>24.86597510173064</v>
       </c>
       <c r="P38" t="n">
-        <v>298.5546630557568</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>143.7362672420583</v>
+        <v>480.7362672420583</v>
       </c>
       <c r="R38" t="n">
         <v>294.54111633436</v>
@@ -10893,7 +10893,7 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L39" t="n">
-        <v>351.3882199259239</v>
+        <v>388.0893364597981</v>
       </c>
       <c r="M39" t="n">
         <v>471.6948204301074</v>
@@ -10905,7 +10905,7 @@
         <v>382.6817988009037</v>
       </c>
       <c r="P39" t="n">
-        <v>219.1507118405495</v>
+        <v>182.4495953066751</v>
       </c>
       <c r="Q39" t="n">
         <v>17.27519534353338</v>
@@ -11045,19 +11045,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J41" t="n">
-        <v>12.18253890840691</v>
+        <v>349.1825389084069</v>
       </c>
       <c r="K41" t="n">
         <v>302.7380854271357</v>
       </c>
       <c r="L41" t="n">
-        <v>294.4950653266332</v>
+        <v>242.4335667662284</v>
       </c>
       <c r="M41" t="n">
-        <v>781.9056994336712</v>
+        <v>496.9671979940761</v>
       </c>
       <c r="N41" t="n">
-        <v>766.1887470145589</v>
+        <v>429.1887470145588</v>
       </c>
       <c r="O41" t="n">
         <v>24.86597510173064</v>
@@ -11066,7 +11066,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>143.7362672420583</v>
+        <v>480.7362672420583</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11285,16 +11285,16 @@
         <v>349.1825389084069</v>
       </c>
       <c r="K44" t="n">
-        <v>302.7380854271357</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>242.4335667662284</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>496.9671979940761</v>
+        <v>833.9671979940761</v>
       </c>
       <c r="N44" t="n">
-        <v>766.1887470145589</v>
+        <v>637.3603992079229</v>
       </c>
       <c r="O44" t="n">
         <v>24.86597510173064</v>
@@ -11303,7 +11303,7 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>143.7362672420583</v>
+        <v>480.7362672420583</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -11361,13 +11361,13 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J45" t="n">
-        <v>190.7636253939142</v>
+        <v>227.4647419277884</v>
       </c>
       <c r="K45" t="n">
         <v>295.8802408630135</v>
       </c>
       <c r="L45" t="n">
-        <v>388.0893364597981</v>
+        <v>351.3882199259239</v>
       </c>
       <c r="M45" t="n">
         <v>471.6948204301074</v>
@@ -22569,10 +22569,10 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>24.28670755036725</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>24.2867075503672</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
@@ -22703,10 +22703,10 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>2.72761134073528</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.727611340735251</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -22755,7 +22755,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>3.339155739849787</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -22803,10 +22803,10 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>24.28670755036717</v>
       </c>
       <c r="U5" t="n">
-        <v>20.94755181051744</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -22940,13 +22940,13 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2.72761134073528</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.727611340735251</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -22992,7 +22992,7 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>1.00190755036732</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -23037,7 +23037,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.001907550367349</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -23223,16 +23223,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>56.93883417786162</v>
       </c>
       <c r="C11" t="n">
-        <v>42.2363888312118</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>10.33915573984979</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>4.363289606868648</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>4.889628708011855</v>
@@ -23517,13 +23517,13 @@
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>61.82846288594232</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>61.82846288587479</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -23748,7 +23748,7 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>5.838651177425447</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
         <v>0</v>
@@ -23766,7 +23766,7 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>5.838651177359168</v>
       </c>
     </row>
     <row r="18">
@@ -23946,13 +23946,13 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>0.8896287080118555</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7494253121827501</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -23985,7 +23985,7 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>5.089225865247999</v>
+        <v>4.949022469351576</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
@@ -24183,7 +24183,7 @@
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8896287080118555</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -24222,13 +24222,13 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>5.838651177361754</v>
       </c>
       <c r="T23" t="n">
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>4.949022469413961</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -24420,13 +24420,13 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>48.88962870801186</v>
       </c>
       <c r="G26" t="n">
-        <v>47.48802555334788</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>9.860943011890846</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -24459,13 +24459,13 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>132.7104291088556</v>
+        <v>42.77025163245675</v>
       </c>
       <c r="T26" t="n">
         <v>229.4965164019308</v>
       </c>
       <c r="U26" t="n">
-        <v>293.1997488099172</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -24474,10 +24474,10 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>236.2818334606677</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>155.3174326828064</v>
       </c>
     </row>
     <row r="27">
@@ -24596,25 +24596,25 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>49.58503799384476</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>145.6925786156646</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>126.8878524473682</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>316.835307164343</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>9.722266425597979</v>
+        <v>9.722266425582745</v>
       </c>
       <c r="R28" t="n">
-        <v>20.49979807044537</v>
+        <v>15.16963617785711</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -24645,19 +24645,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>119.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C29" t="n">
         <v>87.47457824299391</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>48.33915573984979</v>
       </c>
       <c r="E29" t="n">
         <v>42.36328960686865</v>
       </c>
       <c r="F29" t="n">
-        <v>42.88962870801186</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
         <v>41.48802555334787</v>
@@ -24696,13 +24696,13 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>126.7104291088556</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>223.4965164019307</v>
       </c>
       <c r="U29" t="n">
-        <v>251.2896163517989</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -24711,7 +24711,7 @@
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>15.63245676468063</v>
       </c>
       <c r="Y29" t="n">
         <v>0</v>
@@ -24833,13 +24833,13 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>43.58503799384475</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>53.61613838357446</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>190.6963703536521</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -24848,10 +24848,10 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.722266425597999</v>
+        <v>3.722266425582651</v>
       </c>
       <c r="R31" t="n">
-        <v>297.067182908982</v>
+        <v>9.169636177857022</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -24939,13 +24939,13 @@
         <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>2.048307550298631</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>2.048307550367298</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
         <v>0</v>
@@ -25170,7 +25170,7 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>1.874751810517384</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
         <v>0</v>
@@ -25188,7 +25188,7 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.874751810517566</v>
       </c>
     </row>
     <row r="36">
@@ -25310,13 +25310,13 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>1.654811340587621</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>1.654811340735392</v>
       </c>
       <c r="P37" t="n">
         <v>0</v>
@@ -25407,13 +25407,13 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>1.874751810517623</v>
       </c>
       <c r="T38" t="n">
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>1.874751810517637</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -25547,7 +25547,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>1.654811340735286</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
@@ -25562,7 +25562,7 @@
         <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.654811340735478</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -25608,7 +25608,7 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>90.48802555334787</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -25644,10 +25644,10 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>175.7104291088556</v>
       </c>
       <c r="T41" t="n">
-        <v>272.4965164019307</v>
+        <v>161.677379792597</v>
       </c>
       <c r="U41" t="n">
         <v>336.1997488099172</v>
@@ -25656,13 +25656,13 @@
         <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>74.41491727500855</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>279.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>198.3174326828064</v>
       </c>
     </row>
     <row r="42">
@@ -25787,22 +25787,22 @@
         <v>188.6925786156646</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>239.6963703536521</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>60.80657492941133</v>
       </c>
       <c r="P43" t="n">
         <v>22.83530716434304</v>
       </c>
       <c r="Q43" t="n">
-        <v>318.9572893828553</v>
+        <v>65.72226642559799</v>
       </c>
       <c r="R43" t="n">
         <v>71.16963617787238</v>
       </c>
       <c r="S43" t="n">
-        <v>47.26792232580625</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -25833,22 +25833,22 @@
         <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>142.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>97.36328960686865</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>96.48802555334787</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>98.25121146734651</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -25881,16 +25881,16 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>181.7104291088556</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>278.4965164019307</v>
       </c>
       <c r="U44" t="n">
-        <v>5.1997488099172</v>
+        <v>251.4855928922433</v>
       </c>
       <c r="V44" t="n">
-        <v>104.9972494395373</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
         <v>331.3734759809475</v>
@@ -26018,28 +26018,28 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>98.58503799384475</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>194.6925786156646</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>70.56061821489757</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>28.83530716434304</v>
+        <v>365.835307164343</v>
       </c>
       <c r="Q46" t="n">
-        <v>382.2925789241986</v>
+        <v>71.72226642559799</v>
       </c>
       <c r="R46" t="n">
-        <v>414.1696361778723</v>
+        <v>77.16963617787238</v>
       </c>
       <c r="S46" t="n">
-        <v>53.26792232580625</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
@@ -26086,7 +26086,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>871935.3373781985</v>
+        <v>871935.3373781979</v>
       </c>
     </row>
     <row r="3">
@@ -26110,7 +26110,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3042199.883195803</v>
+        <v>3042199.883195808</v>
       </c>
     </row>
     <row r="6">
@@ -26118,7 +26118,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>3763511.792640755</v>
+        <v>3763511.792640764</v>
       </c>
     </row>
     <row r="7">
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4487386.355767607</v>
+        <v>4487386.355767618</v>
       </c>
     </row>
     <row r="8">
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5211260.918894455</v>
+        <v>5211260.918894469</v>
       </c>
     </row>
     <row r="9">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5935135.482021304</v>
+        <v>5935135.48202132</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6620588.567247885</v>
+        <v>6620588.567247906</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7311801.324348018</v>
+        <v>7311801.324348044</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>8034826.961471943</v>
+        <v>8034826.961471977</v>
       </c>
     </row>
     <row r="13">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8757338.443149051</v>
+        <v>8757338.443149077</v>
       </c>
     </row>
     <row r="14">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>9481371.597553428</v>
+        <v>9481371.597553454</v>
       </c>
     </row>
     <row r="15">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>10132795.10699747</v>
+        <v>10132795.1069975</v>
       </c>
     </row>
     <row r="16">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>10778482.54055506</v>
+        <v>10778482.54055509</v>
       </c>
     </row>
   </sheetData>
@@ -26275,34 +26275,34 @@
         <v>1477419.567993805</v>
       </c>
       <c r="D2" t="n">
-        <v>1479674.313977614</v>
+        <v>1479674.313977615</v>
       </c>
       <c r="E2" t="n">
-        <v>1473985.206257077</v>
+        <v>1473985.206257083</v>
       </c>
       <c r="F2" t="n">
-        <v>1473985.206257077</v>
+        <v>1473985.206257084</v>
       </c>
       <c r="G2" t="n">
-        <v>1479221.933346176</v>
+        <v>1479221.933346182</v>
       </c>
       <c r="H2" t="n">
-        <v>1479221.933346175</v>
+        <v>1479221.933346181</v>
       </c>
       <c r="I2" t="n">
-        <v>1479221.933346176</v>
+        <v>1479221.933346181</v>
       </c>
       <c r="J2" t="n">
-        <v>1403316.967360253</v>
+        <v>1403316.967360262</v>
       </c>
       <c r="K2" t="n">
-        <v>1412478.242769842</v>
+        <v>1412478.242769851</v>
       </c>
       <c r="L2" t="n">
-        <v>1479576.444185614</v>
+        <v>1479576.44418562</v>
       </c>
       <c r="M2" t="n">
-        <v>1479546.011174157</v>
+        <v>1479546.011174153</v>
       </c>
       <c r="N2" t="n">
         <v>1479546.011174153</v>
@@ -26330,7 +26330,7 @@
         <v>2112</v>
       </c>
       <c r="E3" t="n">
-        <v>316864</v>
+        <v>316864.0000000062</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>662429.5962486186</v>
+        <v>662414.3467159418</v>
       </c>
       <c r="C4" t="n">
-        <v>660385.8053318616</v>
+        <v>660370.5557991849</v>
       </c>
       <c r="D4" t="n">
-        <v>659247.423067487</v>
+        <v>659232.0843253952</v>
       </c>
       <c r="E4" t="n">
-        <v>654268.4461200004</v>
+        <v>654253.0057269325</v>
       </c>
       <c r="F4" t="n">
-        <v>652232.3336778828</v>
+        <v>652216.8932848147</v>
       </c>
       <c r="G4" t="n">
-        <v>652687.3325291141</v>
+        <v>652671.892136046</v>
       </c>
       <c r="H4" t="n">
-        <v>650635.2986551891</v>
+        <v>650619.858262121</v>
       </c>
       <c r="I4" t="n">
-        <v>648580.4001086702</v>
+        <v>648564.959715602</v>
       </c>
       <c r="J4" t="n">
-        <v>610931.7837333367</v>
+        <v>610916.4740343853</v>
       </c>
       <c r="K4" t="n">
-        <v>613319.6582398718</v>
+        <v>613304.3485409205</v>
       </c>
       <c r="L4" t="n">
-        <v>642943.0329629186</v>
+        <v>642927.8279435942</v>
       </c>
       <c r="M4" t="n">
-        <v>641094.9469295305</v>
+        <v>641079.8977069283</v>
       </c>
       <c r="N4" t="n">
-        <v>639005.4144827749</v>
+        <v>638990.3652601747</v>
       </c>
       <c r="O4" t="n">
-        <v>568368.0107265246</v>
+        <v>568352.9615039246</v>
       </c>
       <c r="P4" t="n">
-        <v>561149.5779135363</v>
+        <v>561134.5286909363</v>
       </c>
     </row>
     <row r="5">
@@ -26434,28 +26434,28 @@
         <v>57078.283</v>
       </c>
       <c r="E5" t="n">
-        <v>56915.39999999999</v>
+        <v>56915.40000000107</v>
       </c>
       <c r="F5" t="n">
-        <v>56915.39999999999</v>
+        <v>56915.40000000107</v>
       </c>
       <c r="G5" t="n">
-        <v>57251.67600000001</v>
+        <v>57251.67600000108</v>
       </c>
       <c r="H5" t="n">
-        <v>57251.67600000001</v>
+        <v>57251.67600000108</v>
       </c>
       <c r="I5" t="n">
-        <v>57251.67600000001</v>
+        <v>57251.67600000108</v>
       </c>
       <c r="J5" t="n">
-        <v>52669.164</v>
+        <v>52669.16400000108</v>
       </c>
       <c r="K5" t="n">
-        <v>53173.57799999999</v>
+        <v>53173.57800000107</v>
       </c>
       <c r="L5" t="n">
-        <v>56844.09</v>
+        <v>56844.09000000107</v>
       </c>
       <c r="M5" t="n">
         <v>56670.697</v>
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>565559.4887451865</v>
+        <v>565574.7382778632</v>
       </c>
       <c r="C6" t="n">
-        <v>760320.2796619434</v>
+        <v>760335.5291946199</v>
       </c>
       <c r="D6" t="n">
-        <v>761236.6079101269</v>
+        <v>761251.9466522194</v>
       </c>
       <c r="E6" t="n">
-        <v>445937.3601370769</v>
+        <v>445952.8005301435</v>
       </c>
       <c r="F6" t="n">
-        <v>764837.4725791943</v>
+        <v>764852.9129722684</v>
       </c>
       <c r="G6" t="n">
-        <v>760482.924817062</v>
+        <v>760498.365210135</v>
       </c>
       <c r="H6" t="n">
-        <v>771334.9586909858</v>
+        <v>771350.3990840591</v>
       </c>
       <c r="I6" t="n">
-        <v>773389.8572375056</v>
+        <v>773405.2976305776</v>
       </c>
       <c r="J6" t="n">
-        <v>345092.0196269167</v>
+        <v>345107.3293258759</v>
       </c>
       <c r="K6" t="n">
-        <v>741185.0065299704</v>
+        <v>741200.3162289298</v>
       </c>
       <c r="L6" t="n">
-        <v>732589.3212226951</v>
+        <v>732604.526242025</v>
       </c>
       <c r="M6" t="n">
-        <v>779380.3672446265</v>
+        <v>779395.4164672242</v>
       </c>
       <c r="N6" t="n">
-        <v>783869.8996913777</v>
+        <v>783884.9489139781</v>
       </c>
       <c r="O6" t="n">
-        <v>518537.9724417304</v>
+        <v>518553.02166433</v>
       </c>
       <c r="P6" t="n">
-        <v>710539.272878041</v>
+        <v>710554.3221006411</v>
       </c>
     </row>
   </sheetData>
@@ -26868,28 +26868,28 @@
         <v>352</v>
       </c>
       <c r="E4" t="n">
-        <v>359</v>
+        <v>359.0000000000177</v>
       </c>
       <c r="F4" t="n">
-        <v>359</v>
+        <v>359.0000000000177</v>
       </c>
       <c r="G4" t="n">
-        <v>359</v>
+        <v>359.0000000000177</v>
       </c>
       <c r="H4" t="n">
-        <v>359</v>
+        <v>359.0000000000177</v>
       </c>
       <c r="I4" t="n">
-        <v>359</v>
+        <v>359.0000000000177</v>
       </c>
       <c r="J4" t="n">
-        <v>350</v>
+        <v>350.0000000000177</v>
       </c>
       <c r="K4" t="n">
-        <v>350</v>
+        <v>350.0000000000177</v>
       </c>
       <c r="L4" t="n">
-        <v>344</v>
+        <v>344.0000000000177</v>
       </c>
       <c r="M4" t="n">
         <v>337</v>
@@ -26975,10 +26975,10 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
         <v>393</v>
@@ -26990,10 +26990,10 @@
         <v>11</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>345</v>
@@ -27008,7 +27008,7 @@
         <v>3</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O2" t="n">
         <v>245</v>
@@ -27079,13 +27079,13 @@
         <v>346</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D4" t="n">
         <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>7</v>
+        <v>7.000000000010633</v>
       </c>
       <c r="F4" t="n">
         <v>-0</v>
@@ -27097,7 +27097,7 @@
         <v>-0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J4" t="n">
         <v>337</v>
@@ -27326,7 +27326,7 @@
         <v>6</v>
       </c>
       <c r="M4" t="n">
-        <v>7</v>
+        <v>7.000000000017735</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -27515,7 +27515,7 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C3" t="n">
-        <v>361.0999124455193</v>
+        <v>295.9271502476842</v>
       </c>
       <c r="D3" t="n">
         <v>347.9376868977026</v>
@@ -27530,7 +27530,7 @@
         <v>325.5954226674802</v>
       </c>
       <c r="H3" t="n">
-        <v>330.7762569977419</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -27560,10 +27560,10 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>300.1638204624224</v>
+        <v>407</v>
       </c>
       <c r="S3" t="n">
-        <v>117.8871603419698</v>
+        <v>407</v>
       </c>
       <c r="T3" t="n">
         <v>58.77688785902325</v>
@@ -27591,13 +27591,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>287.1138003370787</v>
+        <v>407</v>
       </c>
       <c r="C4" t="n">
-        <v>272.7252466480447</v>
+        <v>407</v>
       </c>
       <c r="D4" t="n">
-        <v>285.5362180555555</v>
+        <v>407</v>
       </c>
       <c r="E4" t="n">
         <v>407</v>
@@ -27606,22 +27606,22 @@
         <v>407</v>
       </c>
       <c r="G4" t="n">
-        <v>407</v>
+        <v>313.134399369474</v>
       </c>
       <c r="H4" t="n">
-        <v>407</v>
+        <v>227.6969293803072</v>
       </c>
       <c r="I4" t="n">
         <v>173.0000785709379</v>
       </c>
       <c r="J4" t="n">
-        <v>372.7269980162357</v>
+        <v>26.72699801623563</v>
       </c>
       <c r="K4" t="n">
-        <v>407</v>
+        <v>274.4837246208152</v>
       </c>
       <c r="L4" t="n">
-        <v>407</v>
+        <v>405.5850379938448</v>
       </c>
       <c r="M4" t="n">
         <v>407</v>
@@ -27645,22 +27645,22 @@
         <v>360.2679223258062</v>
       </c>
       <c r="T4" t="n">
-        <v>243.5328460978511</v>
+        <v>209.508336998061</v>
       </c>
       <c r="U4" t="n">
+        <v>150.9518011105235</v>
+      </c>
+      <c r="V4" t="n">
         <v>407</v>
       </c>
-      <c r="V4" t="n">
-        <v>199.1703102162162</v>
-      </c>
       <c r="W4" t="n">
-        <v>226.3728098387097</v>
+        <v>407</v>
       </c>
       <c r="X4" t="n">
-        <v>247.4436454301076</v>
+        <v>407</v>
       </c>
       <c r="Y4" t="n">
-        <v>287.4653528494624</v>
+        <v>407</v>
       </c>
     </row>
     <row r="5">
@@ -27755,7 +27755,7 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
-        <v>267.4490732611911</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -27803,10 +27803,10 @@
         <v>407</v>
       </c>
       <c r="T6" t="n">
-        <v>404.7768878590232</v>
+        <v>324.2882742225231</v>
       </c>
       <c r="U6" t="n">
-        <v>400.2008786281113</v>
+        <v>54.20087862811128</v>
       </c>
       <c r="V6" t="n">
         <v>407</v>
@@ -27818,7 +27818,7 @@
         <v>407</v>
       </c>
       <c r="Y6" t="n">
-        <v>53.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="7">
@@ -27834,16 +27834,16 @@
         <v>272.7252466480447</v>
       </c>
       <c r="D7" t="n">
-        <v>294.8769269415662</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E7" t="n">
-        <v>407</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F7" t="n">
-        <v>407</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G7" t="n">
-        <v>407</v>
+        <v>244.9230531693989</v>
       </c>
       <c r="H7" t="n">
         <v>407</v>
@@ -27879,16 +27879,16 @@
         <v>407</v>
       </c>
       <c r="S7" t="n">
+        <v>360.2679223258062</v>
+      </c>
+      <c r="T7" t="n">
+        <v>222.4164209109078</v>
+      </c>
+      <c r="U7" t="n">
         <v>407</v>
       </c>
-      <c r="T7" t="n">
-        <v>209.508336998061</v>
-      </c>
-      <c r="U7" t="n">
-        <v>150.9518011105235</v>
-      </c>
       <c r="V7" t="n">
-        <v>199.1703102162162</v>
+        <v>407</v>
       </c>
       <c r="W7" t="n">
         <v>226.3728098387097</v>
@@ -27989,13 +27989,13 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C9" t="n">
-        <v>361.0999124455193</v>
+        <v>293.8691790540182</v>
       </c>
       <c r="D9" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>124.62163269442</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>339.6362423378769</v>
@@ -28034,7 +28034,7 @@
         <v>154.6833405621777</v>
       </c>
       <c r="R9" t="n">
-        <v>186.3261369150208</v>
+        <v>407</v>
       </c>
       <c r="S9" t="n">
         <v>407</v>
@@ -28043,13 +28043,13 @@
         <v>404.7768878590232</v>
       </c>
       <c r="U9" t="n">
-        <v>400.2008786281113</v>
+        <v>48.20087862810437</v>
       </c>
       <c r="V9" t="n">
-        <v>62.51066719152016</v>
+        <v>407</v>
       </c>
       <c r="W9" t="n">
-        <v>80.37314290982852</v>
+        <v>407</v>
       </c>
       <c r="X9" t="n">
         <v>407</v>
@@ -28077,7 +28077,7 @@
         <v>407</v>
       </c>
       <c r="F10" t="n">
-        <v>407</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G10" t="n">
         <v>244.9230531693989</v>
@@ -28089,7 +28089,7 @@
         <v>173.0000785709379</v>
       </c>
       <c r="J10" t="n">
-        <v>352.2469796754786</v>
+        <v>378.7269980162426</v>
       </c>
       <c r="K10" t="n">
         <v>407</v>
@@ -28122,7 +28122,7 @@
         <v>209.508336998061</v>
       </c>
       <c r="U10" t="n">
-        <v>150.9518011105235</v>
+        <v>257.0889268020177</v>
       </c>
       <c r="V10" t="n">
         <v>199.1703102162162</v>
@@ -28223,7 +28223,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>25.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C12" t="n">
         <v>361.0999124455193</v>
@@ -28232,7 +28232,7 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E12" t="n">
-        <v>342.6720972219126</v>
+        <v>274.0556465008884</v>
       </c>
       <c r="F12" t="n">
         <v>339.6362423378769</v>
@@ -28241,7 +28241,7 @@
         <v>325.5954226674802</v>
       </c>
       <c r="H12" t="n">
-        <v>330.7762569977419</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>212.1645934385184</v>
@@ -28268,22 +28268,22 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>154.6833405621777</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
+        <v>179.3261369150035</v>
+      </c>
+      <c r="S12" t="n">
+        <v>104.8871603419516</v>
+      </c>
+      <c r="T12" t="n">
         <v>400</v>
-      </c>
-      <c r="S12" t="n">
-        <v>400</v>
-      </c>
-      <c r="T12" t="n">
-        <v>45.77688785902325</v>
       </c>
       <c r="U12" t="n">
         <v>400</v>
       </c>
       <c r="V12" t="n">
-        <v>55.51066719152016</v>
+        <v>400</v>
       </c>
       <c r="W12" t="n">
         <v>400</v>
@@ -28292,7 +28292,7 @@
         <v>400</v>
       </c>
       <c r="Y12" t="n">
-        <v>387.2410866916023</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="13">
@@ -28311,7 +28311,7 @@
         <v>400</v>
       </c>
       <c r="E13" t="n">
-        <v>400</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F13" t="n">
         <v>400</v>
@@ -28320,13 +28320,13 @@
         <v>244.9230531693989</v>
       </c>
       <c r="H13" t="n">
-        <v>227.6969293803072</v>
+        <v>295.2442750737916</v>
       </c>
       <c r="I13" t="n">
         <v>173.0000785709379</v>
       </c>
       <c r="J13" t="n">
-        <v>385.7269980162357</v>
+        <v>385.726998016252</v>
       </c>
       <c r="K13" t="n">
         <v>400</v>
@@ -28353,22 +28353,22 @@
         <v>400</v>
       </c>
       <c r="S13" t="n">
+        <v>360.2679223258062</v>
+      </c>
+      <c r="T13" t="n">
         <v>400</v>
-      </c>
-      <c r="T13" t="n">
-        <v>260.5228376423723</v>
       </c>
       <c r="U13" t="n">
         <v>150.9518011105235</v>
       </c>
       <c r="V13" t="n">
-        <v>400</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W13" t="n">
         <v>400</v>
       </c>
       <c r="X13" t="n">
-        <v>247.4436454301076</v>
+        <v>400</v>
       </c>
       <c r="Y13" t="n">
         <v>400</v>
@@ -28469,7 +28469,7 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F15" t="n">
         <v>339.6362423378769</v>
@@ -28508,25 +28508,25 @@
         <v>154.6833405621777</v>
       </c>
       <c r="R15" t="n">
+        <v>179.3261369150089</v>
+      </c>
+      <c r="S15" t="n">
+        <v>254.099566241391</v>
+      </c>
+      <c r="T15" t="n">
         <v>400</v>
       </c>
-      <c r="S15" t="n">
-        <v>366.1697188935132</v>
-      </c>
-      <c r="T15" t="n">
-        <v>45.77688785902325</v>
-      </c>
       <c r="U15" t="n">
-        <v>400</v>
+        <v>41.20087862810124</v>
       </c>
       <c r="V15" t="n">
-        <v>400</v>
+        <v>55.51066719151012</v>
       </c>
       <c r="W15" t="n">
         <v>400</v>
       </c>
       <c r="X15" t="n">
-        <v>60.86273944538755</v>
+        <v>400</v>
       </c>
       <c r="Y15" t="n">
         <v>399.3913927661343</v>
@@ -28539,34 +28539,34 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>400</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C16" t="n">
         <v>272.7252466480447</v>
       </c>
       <c r="D16" t="n">
-        <v>400</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E16" t="n">
         <v>280.9809048369565</v>
       </c>
       <c r="F16" t="n">
+        <v>274.3828559677419</v>
+      </c>
+      <c r="G16" t="n">
+        <v>381.143263960289</v>
+      </c>
+      <c r="H16" t="n">
         <v>400</v>
       </c>
-      <c r="G16" t="n">
+      <c r="I16" t="n">
         <v>400</v>
       </c>
-      <c r="H16" t="n">
-        <v>227.6969293803072</v>
-      </c>
-      <c r="I16" t="n">
-        <v>173.0000785709379</v>
-      </c>
       <c r="J16" t="n">
-        <v>26.72699801623563</v>
+        <v>385.7269980162457</v>
       </c>
       <c r="K16" t="n">
-        <v>274.4837246208152</v>
+        <v>400</v>
       </c>
       <c r="L16" t="n">
         <v>400</v>
@@ -28593,16 +28593,16 @@
         <v>400</v>
       </c>
       <c r="T16" t="n">
-        <v>400</v>
+        <v>209.508336998061</v>
       </c>
       <c r="U16" t="n">
         <v>400</v>
       </c>
       <c r="V16" t="n">
-        <v>400</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W16" t="n">
-        <v>347.0468628016018</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X16" t="n">
         <v>247.4436454301076</v>
@@ -28633,7 +28633,7 @@
         <v>404</v>
       </c>
       <c r="G17" t="n">
-        <v>404.0000000000052</v>
+        <v>404.0000000000043</v>
       </c>
       <c r="H17" t="n">
         <v>404</v>
@@ -28700,10 +28700,10 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C18" t="n">
-        <v>2.099912445519294</v>
+        <v>297.2823092509116</v>
       </c>
       <c r="D18" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -28757,7 +28757,7 @@
         <v>400.2008786281113</v>
       </c>
       <c r="V18" t="n">
-        <v>351.2447099076893</v>
+        <v>404</v>
       </c>
       <c r="W18" t="n">
         <v>404</v>
@@ -28791,7 +28791,7 @@
         <v>274.3828559677419</v>
       </c>
       <c r="G19" t="n">
-        <v>298.0255668956406</v>
+        <v>244.9230531693989</v>
       </c>
       <c r="H19" t="n">
         <v>227.6969293803072</v>
@@ -28833,10 +28833,10 @@
         <v>404</v>
       </c>
       <c r="U19" t="n">
-        <v>150.9518011105235</v>
+        <v>404.0000000000041</v>
       </c>
       <c r="V19" t="n">
-        <v>404</v>
+        <v>204.0543148367613</v>
       </c>
       <c r="W19" t="n">
         <v>404</v>
@@ -28937,13 +28937,13 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C21" t="n">
-        <v>2.099912445519294</v>
+        <v>2.099912445509247</v>
       </c>
       <c r="D21" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>295.1823968054023</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -28991,7 +28991,7 @@
         <v>404</v>
       </c>
       <c r="U21" t="n">
-        <v>347.4455885358007</v>
+        <v>400.2008786281113</v>
       </c>
       <c r="V21" t="n">
         <v>404</v>
@@ -29034,7 +29034,7 @@
         <v>404</v>
       </c>
       <c r="I22" t="n">
-        <v>404</v>
+        <v>270.7920637679456</v>
       </c>
       <c r="J22" t="n">
         <v>26.72699801623563</v>
@@ -29076,7 +29076,7 @@
         <v>404</v>
       </c>
       <c r="W22" t="n">
-        <v>270.7920637679457</v>
+        <v>404</v>
       </c>
       <c r="X22" t="n">
         <v>247.4436454301076</v>
@@ -29107,7 +29107,7 @@
         <v>404</v>
       </c>
       <c r="G23" t="n">
-        <v>404.000000000005</v>
+        <v>404</v>
       </c>
       <c r="H23" t="n">
         <v>404</v>
@@ -29177,16 +29177,16 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D24" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>272.8401325751698</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>90.86573736756984</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>325.5954226674802</v>
       </c>
       <c r="H24" t="n">
         <v>330.7762569977419</v>
@@ -29216,7 +29216,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>154.6833405621777</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>404</v>
@@ -29240,7 +29240,7 @@
         <v>404</v>
       </c>
       <c r="Y24" t="n">
-        <v>40.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="25">
@@ -29256,13 +29256,13 @@
         <v>272.7252466480447</v>
       </c>
       <c r="D25" t="n">
+        <v>285.5362180555555</v>
+      </c>
+      <c r="E25" t="n">
+        <v>280.9809048369565</v>
+      </c>
+      <c r="F25" t="n">
         <v>404</v>
-      </c>
-      <c r="E25" t="n">
-        <v>404</v>
-      </c>
-      <c r="F25" t="n">
-        <v>274.3828559677419</v>
       </c>
       <c r="G25" t="n">
         <v>404</v>
@@ -29274,10 +29274,10 @@
         <v>404</v>
       </c>
       <c r="J25" t="n">
-        <v>26.72699801623563</v>
+        <v>385.7269980162459</v>
       </c>
       <c r="K25" t="n">
-        <v>274.4837246208152</v>
+        <v>404</v>
       </c>
       <c r="L25" t="n">
         <v>404</v>
@@ -29301,16 +29301,16 @@
         <v>404</v>
       </c>
       <c r="S25" t="n">
-        <v>360.2679223258062</v>
+        <v>404</v>
       </c>
       <c r="T25" t="n">
         <v>209.508336998061</v>
       </c>
       <c r="U25" t="n">
-        <v>404</v>
+        <v>158.9358990916776</v>
       </c>
       <c r="V25" t="n">
-        <v>374.488829286053</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W25" t="n">
         <v>226.3728098387097</v>
@@ -29411,7 +29411,7 @@
         <v>356</v>
       </c>
       <c r="C27" t="n">
-        <v>356</v>
+        <v>11.09991244550413</v>
       </c>
       <c r="D27" t="n">
         <v>347.9376868977026</v>
@@ -29420,13 +29420,13 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F27" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
         <v>325.5954226674802</v>
       </c>
       <c r="H27" t="n">
-        <v>55.74807057474283</v>
+        <v>330.7762569977419</v>
       </c>
       <c r="I27" t="n">
         <v>212.1645934385184</v>
@@ -29456,10 +29456,10 @@
         <v>154.6833405621777</v>
       </c>
       <c r="R27" t="n">
-        <v>188.3261369150208</v>
+        <v>355.7214407263644</v>
       </c>
       <c r="S27" t="n">
-        <v>113.8871603419698</v>
+        <v>356</v>
       </c>
       <c r="T27" t="n">
         <v>356</v>
@@ -29508,13 +29508,13 @@
         <v>356</v>
       </c>
       <c r="I28" t="n">
-        <v>233.6862838375797</v>
+        <v>173.0000785709379</v>
       </c>
       <c r="J28" t="n">
-        <v>26.72699801623563</v>
+        <v>26.96776349516048</v>
       </c>
       <c r="K28" t="n">
-        <v>274.4837246208152</v>
+        <v>356</v>
       </c>
       <c r="L28" t="n">
         <v>356</v>
@@ -29550,10 +29550,10 @@
         <v>356</v>
       </c>
       <c r="W28" t="n">
+        <v>226.3728098387097</v>
+      </c>
+      <c r="X28" t="n">
         <v>356</v>
-      </c>
-      <c r="X28" t="n">
-        <v>247.4436454301076</v>
       </c>
       <c r="Y28" t="n">
         <v>356</v>
@@ -29645,7 +29645,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>34.55655664632661</v>
+        <v>362</v>
       </c>
       <c r="C30" t="n">
         <v>361.0999124455193</v>
@@ -29654,19 +29654,19 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E30" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G30" t="n">
-        <v>325.5954226674802</v>
+        <v>255.1289752756071</v>
       </c>
       <c r="H30" t="n">
-        <v>330.7762569977419</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>212.1645934385184</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -29690,7 +29690,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>154.6833405621777</v>
       </c>
       <c r="R30" t="n">
         <v>362</v>
@@ -29705,7 +29705,7 @@
         <v>362</v>
       </c>
       <c r="V30" t="n">
-        <v>312.3765757428414</v>
+        <v>362</v>
       </c>
       <c r="W30" t="n">
         <v>362</v>
@@ -29727,7 +29727,7 @@
         <v>362</v>
       </c>
       <c r="C31" t="n">
-        <v>362</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D31" t="n">
         <v>362</v>
@@ -29748,10 +29748,10 @@
         <v>362</v>
       </c>
       <c r="J31" t="n">
+        <v>26.72699801623563</v>
+      </c>
+      <c r="K31" t="n">
         <v>362</v>
-      </c>
-      <c r="K31" t="n">
-        <v>274.4837246208152</v>
       </c>
       <c r="L31" t="n">
         <v>362</v>
@@ -29778,16 +29778,16 @@
         <v>362</v>
       </c>
       <c r="T31" t="n">
-        <v>334.1862830141722</v>
+        <v>362</v>
       </c>
       <c r="U31" t="n">
-        <v>150.9518011105235</v>
+        <v>324.5423739200108</v>
       </c>
       <c r="V31" t="n">
         <v>199.1703102162162</v>
       </c>
       <c r="W31" t="n">
-        <v>226.3728098387097</v>
+        <v>362</v>
       </c>
       <c r="X31" t="n">
         <v>247.4436454301076</v>
@@ -29851,7 +29851,7 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>233.9592470695005</v>
+        <v>233.959247069458</v>
       </c>
       <c r="S32" t="n">
         <v>410</v>
@@ -29882,7 +29882,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>40.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C33" t="n">
         <v>361.0999124455193</v>
@@ -29894,13 +29894,13 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F33" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
         <v>325.5954226674802</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>330.7762569977419</v>
       </c>
       <c r="I33" t="n">
         <v>212.1645934385184</v>
@@ -29930,13 +29930,13 @@
         <v>154.6833405621777</v>
       </c>
       <c r="R33" t="n">
-        <v>410</v>
+        <v>267.7137287995525</v>
       </c>
       <c r="S33" t="n">
-        <v>410</v>
+        <v>119.8871603419552</v>
       </c>
       <c r="T33" t="n">
-        <v>404.7768878590232</v>
+        <v>60.77688785900861</v>
       </c>
       <c r="U33" t="n">
         <v>400.2008786281113</v>
@@ -29948,10 +29948,10 @@
         <v>410</v>
       </c>
       <c r="X33" t="n">
-        <v>312.740903801469</v>
+        <v>410</v>
       </c>
       <c r="Y33" t="n">
-        <v>55.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="34">
@@ -29970,28 +29970,28 @@
         <v>410</v>
       </c>
       <c r="E34" t="n">
+        <v>280.9809048369565</v>
+      </c>
+      <c r="F34" t="n">
         <v>410</v>
       </c>
-      <c r="F34" t="n">
-        <v>398.4547593695517</v>
-      </c>
       <c r="G34" t="n">
-        <v>244.9230531693989</v>
+        <v>410</v>
       </c>
       <c r="H34" t="n">
-        <v>227.6969293803072</v>
+        <v>410</v>
       </c>
       <c r="I34" t="n">
         <v>173.0000785709379</v>
       </c>
       <c r="J34" t="n">
-        <v>26.72699801623563</v>
+        <v>370.7269980162502</v>
       </c>
       <c r="K34" t="n">
-        <v>274.4837246208152</v>
+        <v>410</v>
       </c>
       <c r="L34" t="n">
-        <v>405.5850379938448</v>
+        <v>410</v>
       </c>
       <c r="M34" t="n">
         <v>410</v>
@@ -30015,22 +30015,22 @@
         <v>360.2679223258062</v>
       </c>
       <c r="T34" t="n">
-        <v>410</v>
+        <v>209.508336998061</v>
       </c>
       <c r="U34" t="n">
-        <v>410</v>
+        <v>168.5764954934218</v>
       </c>
       <c r="V34" t="n">
-        <v>410</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W34" t="n">
-        <v>410</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X34" t="n">
         <v>247.4436454301076</v>
       </c>
       <c r="Y34" t="n">
-        <v>287.4653528494624</v>
+        <v>410</v>
       </c>
     </row>
     <row r="35">
@@ -30128,13 +30128,13 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E36" t="n">
-        <v>342.6720972219126</v>
+        <v>5.672097221912622</v>
       </c>
       <c r="F36" t="n">
-        <v>333.6049456651013</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G36" t="n">
-        <v>325.5954226674802</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
         <v>330.7762569977419</v>
@@ -30167,16 +30167,16 @@
         <v>154.6833405621777</v>
       </c>
       <c r="R36" t="n">
-        <v>201.3261369150208</v>
+        <v>413</v>
       </c>
       <c r="S36" t="n">
-        <v>413</v>
+        <v>183.8902629097254</v>
       </c>
       <c r="T36" t="n">
-        <v>67.77688785902325</v>
+        <v>404.7768878590232</v>
       </c>
       <c r="U36" t="n">
-        <v>63.20087862811128</v>
+        <v>400.2008786281113</v>
       </c>
       <c r="V36" t="n">
         <v>413</v>
@@ -30204,19 +30204,19 @@
         <v>413</v>
       </c>
       <c r="D37" t="n">
+        <v>285.5362180555555</v>
+      </c>
+      <c r="E37" t="n">
+        <v>280.9809048369565</v>
+      </c>
+      <c r="F37" t="n">
         <v>413</v>
       </c>
-      <c r="E37" t="n">
-        <v>384.2608892107804</v>
-      </c>
-      <c r="F37" t="n">
-        <v>274.3828559677419</v>
-      </c>
       <c r="G37" t="n">
-        <v>244.9230531693989</v>
+        <v>413</v>
       </c>
       <c r="H37" t="n">
-        <v>227.6969293803072</v>
+        <v>413</v>
       </c>
       <c r="I37" t="n">
         <v>173.0000785709379</v>
@@ -30225,7 +30225,7 @@
         <v>26.72699801623563</v>
       </c>
       <c r="K37" t="n">
-        <v>413</v>
+        <v>274.4837246208152</v>
       </c>
       <c r="L37" t="n">
         <v>413</v>
@@ -30249,19 +30249,19 @@
         <v>413</v>
       </c>
       <c r="S37" t="n">
-        <v>360.2679223258062</v>
+        <v>413</v>
       </c>
       <c r="T37" t="n">
-        <v>209.508336998061</v>
+        <v>413</v>
       </c>
       <c r="U37" t="n">
-        <v>150.9518011105235</v>
+        <v>172.4478205942152</v>
       </c>
       <c r="V37" t="n">
-        <v>413</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W37" t="n">
-        <v>413</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X37" t="n">
         <v>413</v>
@@ -30359,13 +30359,13 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C39" t="n">
-        <v>24.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D39" t="n">
-        <v>347.9376868977026</v>
+        <v>197.9570303572016</v>
       </c>
       <c r="E39" t="n">
-        <v>342.6720972219126</v>
+        <v>5.672097221912622</v>
       </c>
       <c r="F39" t="n">
         <v>339.6362423378769</v>
@@ -30374,7 +30374,7 @@
         <v>325.5954226674802</v>
       </c>
       <c r="H39" t="n">
-        <v>330.7762569977419</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
         <v>212.1645934385184</v>
@@ -30410,10 +30410,10 @@
         <v>126.8871603419698</v>
       </c>
       <c r="T39" t="n">
-        <v>67.77688785902325</v>
+        <v>404.7768878590232</v>
       </c>
       <c r="U39" t="n">
-        <v>256.4439650898685</v>
+        <v>400.2008786281113</v>
       </c>
       <c r="V39" t="n">
         <v>413</v>
@@ -30438,7 +30438,7 @@
         <v>287.1138003370787</v>
       </c>
       <c r="C40" t="n">
-        <v>272.7252466480447</v>
+        <v>413</v>
       </c>
       <c r="D40" t="n">
         <v>285.5362180555555</v>
@@ -30447,13 +30447,13 @@
         <v>280.9809048369565</v>
       </c>
       <c r="F40" t="n">
-        <v>274.3828559677419</v>
+        <v>413</v>
       </c>
       <c r="G40" t="n">
-        <v>244.9230531693989</v>
+        <v>398.2716071994867</v>
       </c>
       <c r="H40" t="n">
-        <v>308.6993393938293</v>
+        <v>227.6969293803072</v>
       </c>
       <c r="I40" t="n">
         <v>413</v>
@@ -30465,7 +30465,7 @@
         <v>413</v>
       </c>
       <c r="L40" t="n">
-        <v>413</v>
+        <v>405.5850379938448</v>
       </c>
       <c r="M40" t="n">
         <v>413</v>
@@ -30486,7 +30486,7 @@
         <v>413</v>
       </c>
       <c r="S40" t="n">
-        <v>413</v>
+        <v>360.2679223258062</v>
       </c>
       <c r="T40" t="n">
         <v>209.508336998061</v>
@@ -30501,10 +30501,10 @@
         <v>413</v>
       </c>
       <c r="X40" t="n">
-        <v>413</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y40" t="n">
-        <v>413</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="41">
@@ -30605,7 +30605,7 @@
         <v>313</v>
       </c>
       <c r="F42" t="n">
-        <v>313</v>
+        <v>215.7735812715559</v>
       </c>
       <c r="G42" t="n">
         <v>313</v>
@@ -30638,7 +30638,7 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>57.45692183373355</v>
+        <v>154.6833405621777</v>
       </c>
       <c r="R42" t="n">
         <v>313</v>
@@ -30678,7 +30678,7 @@
         <v>313</v>
       </c>
       <c r="D43" t="n">
-        <v>307.8659044299907</v>
+        <v>313</v>
       </c>
       <c r="E43" t="n">
         <v>313</v>
@@ -30690,7 +30690,7 @@
         <v>313</v>
       </c>
       <c r="H43" t="n">
-        <v>313</v>
+        <v>307.8659044299907</v>
       </c>
       <c r="I43" t="n">
         <v>313</v>
@@ -30875,10 +30875,10 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>147.4569218337334</v>
+        <v>154.6833405621777</v>
       </c>
       <c r="R45" t="n">
-        <v>307</v>
+        <v>299.7735812715558</v>
       </c>
       <c r="S45" t="n">
         <v>307</v>
@@ -34743,28 +34743,28 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>346</v>
       </c>
       <c r="K2" t="n">
-        <v>332.0202020202022</v>
+        <v>34.26191457286433</v>
       </c>
       <c r="L2" t="n">
+        <v>42.50493467336685</v>
+      </c>
+      <c r="M2" t="n">
         <v>346</v>
       </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>346</v>
       </c>
       <c r="P2" t="n">
-        <v>346</v>
+        <v>38.44533694424321</v>
       </c>
       <c r="Q2" t="n">
-        <v>346</v>
+        <v>216.8080158297276</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34822,7 +34822,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>137.7593910760456</v>
+        <v>137.7593910760142</v>
       </c>
       <c r="K3" t="n">
         <v>214.3749772823007</v>
@@ -34877,13 +34877,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>119.8861996629213</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>134.2747533519553</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>121.4637819444445</v>
       </c>
       <c r="E4" t="n">
         <v>126.0190951630435</v>
@@ -34892,22 +34892,22 @@
         <v>132.6171440322581</v>
       </c>
       <c r="G4" t="n">
-        <v>162.0769468306011</v>
+        <v>68.21134620007513</v>
       </c>
       <c r="H4" t="n">
-        <v>179.3030706196928</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>346</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>132.5162753791848</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>1.414962006155235</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -34931,22 +34931,22 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>34.02450909979009</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>256.0481988894765</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>207.8296897837838</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>180.6271901612903</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>159.5563545698924</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>119.5346471505376</v>
       </c>
     </row>
     <row r="5">
@@ -34989,10 +34989,10 @@
         <v>346</v>
       </c>
       <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
         <v>293.5748650759587</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -35077,7 +35077,7 @@
         <v>275.7452200159539</v>
       </c>
       <c r="P6" t="n">
-        <v>140.1205535039634</v>
+        <v>140.1205535039519</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -35120,16 +35120,16 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>9.340708886010749</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>126.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>132.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>162.0769468306011</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>179.3030706196928</v>
@@ -35144,7 +35144,7 @@
         <v>132.5162753791848</v>
       </c>
       <c r="L7" t="n">
-        <v>1.414962006155235</v>
+        <v>1.414962006155253</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -35165,16 +35165,16 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>46.73207767419376</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>12.90808391284682</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>256.0481988894765</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>207.8296897837838</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
@@ -35226,10 +35226,10 @@
         <v>352</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>352.0000000000069</v>
       </c>
       <c r="N8" t="n">
-        <v>352</v>
+        <v>299.3324408335278</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -35238,7 +35238,7 @@
         <v>38.44533694424321</v>
       </c>
       <c r="Q8" t="n">
-        <v>299.3324408335347</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -35363,7 +35363,7 @@
         <v>126.0190951630435</v>
       </c>
       <c r="F10" t="n">
-        <v>132.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -35375,13 +35375,13 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>325.519981659243</v>
+        <v>352.0000000000069</v>
       </c>
       <c r="K10" t="n">
         <v>132.5162753791848</v>
       </c>
       <c r="L10" t="n">
-        <v>1.414962006155235</v>
+        <v>1.414962006155253</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -35408,7 +35408,7 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>106.1371256914942</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -35454,25 +35454,25 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>306.0496125507063</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>359</v>
+        <v>359.0000000000177</v>
       </c>
       <c r="L11" t="n">
-        <v>359</v>
+        <v>359.0000000000178</v>
       </c>
       <c r="M11" t="n">
-        <v>359</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>359.0000000000164</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>38.44533694424321</v>
+        <v>344.4949494949678</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -35597,7 +35597,7 @@
         <v>114.4637819444445</v>
       </c>
       <c r="E13" t="n">
-        <v>119.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
         <v>125.6171440322581</v>
@@ -35606,13 +35606,13 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>67.54734569348446</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>359</v>
+        <v>359.0000000000164</v>
       </c>
       <c r="K13" t="n">
         <v>125.5162753791848</v>
@@ -35639,22 +35639,22 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>39.73207767419375</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>51.01450064431133</v>
+        <v>190.491663001939</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
         <v>173.6271901612903</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y13" t="n">
         <v>112.5346471505376</v>
@@ -35691,25 +35691,25 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>263.5446778773393</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>359</v>
+        <v>359.0000000000177</v>
       </c>
       <c r="L14" t="n">
-        <v>42.50493467336685</v>
+        <v>359.0000000000178</v>
       </c>
       <c r="M14" t="n">
-        <v>359</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>359</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>344.4949494949724</v>
       </c>
       <c r="P14" t="n">
-        <v>38.44533694424321</v>
+        <v>359.0000000000101</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -35825,34 +35825,34 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>112.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>114.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>155.0769468306011</v>
+        <v>136.2202107908901</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>172.3030706196928</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>226.9999214290621</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>359.0000000000101</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>125.5162753791848</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -35876,19 +35876,19 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>39.73207767419376</v>
+        <v>39.73207767419375</v>
       </c>
       <c r="T16" t="n">
-        <v>190.491663001939</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
         <v>249.0481988894765</v>
       </c>
       <c r="V16" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>120.6740529628921</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -35919,7 +35919,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.511974446657361</v>
+        <v>0.5119744466564515</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -35928,22 +35928,22 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>359</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>359</v>
+        <v>359.0000000000177</v>
       </c>
       <c r="L17" t="n">
-        <v>306.0496125507062</v>
+        <v>359.0000000000178</v>
       </c>
       <c r="M17" t="n">
-        <v>359</v>
+        <v>306.0496125507293</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>359.0000000000101</v>
       </c>
       <c r="P17" t="n">
         <v>38.44533694424321</v>
@@ -36077,7 +36077,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>53.10251372624168</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -36119,10 +36119,10 @@
         <v>194.491663001939</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>253.0481988894806</v>
       </c>
       <c r="V19" t="n">
-        <v>204.8296897837838</v>
+        <v>4.884004620545123</v>
       </c>
       <c r="W19" t="n">
         <v>177.6271901612903</v>
@@ -36165,19 +36165,19 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>359</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>359</v>
+        <v>359.0000000000177</v>
       </c>
       <c r="L20" t="n">
-        <v>306.0496125507062</v>
+        <v>306.049612550737</v>
       </c>
       <c r="M20" t="n">
-        <v>359</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>359.0000000000101</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -36186,7 +36186,7 @@
         <v>38.44533694424321</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>359.0000000000101</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36320,7 +36320,7 @@
         <v>176.3030706196928</v>
       </c>
       <c r="I22" t="n">
-        <v>230.9999214290621</v>
+        <v>97.79198519700761</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -36362,7 +36362,7 @@
         <v>204.8296897837838</v>
       </c>
       <c r="W22" t="n">
-        <v>44.41925392923604</v>
+        <v>177.6271901612903</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -36393,7 +36393,7 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.5119744466571337</v>
+        <v>0.5119744466521314</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -36402,19 +36402,19 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>359.0000000000102</v>
       </c>
       <c r="K23" t="n">
-        <v>34.26191457286432</v>
+        <v>34.26191457286433</v>
       </c>
       <c r="L23" t="n">
-        <v>271.7876979778418</v>
+        <v>271.7876979778816</v>
       </c>
       <c r="M23" t="n">
-        <v>359</v>
+        <v>359.0000000000102</v>
       </c>
       <c r="N23" t="n">
-        <v>359</v>
+        <v>359.0000000000102</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -36423,7 +36423,7 @@
         <v>38.44533694424321</v>
       </c>
       <c r="Q23" t="n">
-        <v>359</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -36542,13 +36542,13 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>118.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>123.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>129.6171440322581</v>
       </c>
       <c r="G25" t="n">
         <v>159.0769468306011</v>
@@ -36560,10 +36560,10 @@
         <v>230.9999214290621</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>359.0000000000102</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>129.5162753791848</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -36587,16 +36587,16 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>43.73207767419375</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>253.0481988894765</v>
+        <v>7.984097981154099</v>
       </c>
       <c r="V25" t="n">
-        <v>175.3185190698368</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
@@ -36639,16 +36639,16 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>350.0000000000152</v>
       </c>
       <c r="K26" t="n">
-        <v>350</v>
+        <v>34.26191457286433</v>
       </c>
       <c r="L26" t="n">
-        <v>335.8585858585859</v>
+        <v>263.1513343415032</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>350.0000000000152</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -36657,10 +36657,10 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>350</v>
+        <v>38.44533694424321</v>
       </c>
       <c r="Q26" t="n">
-        <v>350</v>
+        <v>350.0000000000152</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -36794,13 +36794,13 @@
         <v>128.3030706196928</v>
       </c>
       <c r="I28" t="n">
-        <v>60.68620526664175</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>0.2407654789248677</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>81.51627537918483</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -36836,10 +36836,10 @@
         <v>156.8296897837838</v>
       </c>
       <c r="W28" t="n">
-        <v>129.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>108.5563545698924</v>
       </c>
       <c r="Y28" t="n">
         <v>68.53464715053764</v>
@@ -36876,19 +36876,19 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>350.0000000000153</v>
       </c>
       <c r="K29" t="n">
-        <v>350</v>
+        <v>34.26191457286433</v>
       </c>
       <c r="L29" t="n">
-        <v>350</v>
+        <v>42.50493467336685</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>350.0000000000153</v>
       </c>
       <c r="N29" t="n">
-        <v>350</v>
+        <v>350.0000000000153</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -36897,7 +36897,7 @@
         <v>38.44533694424321</v>
       </c>
       <c r="Q29" t="n">
-        <v>297.4132489143427</v>
+        <v>220.6463996681357</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -37013,7 +37013,7 @@
         <v>74.88619966292134</v>
       </c>
       <c r="C31" t="n">
-        <v>89.27475335195533</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
         <v>76.46378194444452</v>
@@ -37034,10 +37034,10 @@
         <v>188.9999214290621</v>
       </c>
       <c r="J31" t="n">
-        <v>335.2730019837644</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>87.51627537918483</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -37064,16 +37064,16 @@
         <v>1.732077674193746</v>
       </c>
       <c r="T31" t="n">
-        <v>124.6779460161112</v>
+        <v>152.491663001939</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>173.5905728094873</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>135.6271901612903</v>
       </c>
       <c r="X31" t="n">
         <v>0</v>
@@ -37113,31 +37113,31 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>344.0000000000146</v>
       </c>
       <c r="K32" t="n">
-        <v>34.26191457286432</v>
+        <v>344.0000000000177</v>
       </c>
       <c r="L32" t="n">
-        <v>42.50493467336685</v>
+        <v>344.0000000000177</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>291.6556731568296</v>
       </c>
       <c r="N32" t="n">
-        <v>253.334160854779</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>344</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>344</v>
+        <v>38.44533694424321</v>
       </c>
       <c r="Q32" t="n">
-        <v>344</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>-4.248902015858377e-11</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -37192,7 +37192,7 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>138.8241439735248</v>
+        <v>129.840199156935</v>
       </c>
       <c r="K33" t="n">
         <v>214.3749772823007</v>
@@ -37201,7 +37201,7 @@
         <v>305.3822715751021</v>
       </c>
       <c r="M33" t="n">
-        <v>114.4810973478018</v>
+        <v>123.4650421645043</v>
       </c>
       <c r="N33" t="n">
         <v>172.1079935048813</v>
@@ -37256,28 +37256,28 @@
         <v>124.4637819444445</v>
       </c>
       <c r="E34" t="n">
-        <v>129.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>124.0719034018097</v>
+        <v>135.6171440322581</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>165.0769468306011</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>182.3030706196928</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>344.0000000000146</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>135.5162753791848</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>4.414962006155253</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -37301,22 +37301,22 @@
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>200.491663001939</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>259.0481988894765</v>
+        <v>17.62469438289833</v>
       </c>
       <c r="V34" t="n">
-        <v>210.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>183.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>122.5346471505376</v>
       </c>
     </row>
     <row r="35">
@@ -37353,13 +37353,13 @@
         <v>337</v>
       </c>
       <c r="K35" t="n">
+        <v>242.4335667662284</v>
+      </c>
+      <c r="L35" t="n">
+        <v>42.50493467336685</v>
+      </c>
+      <c r="M35" t="n">
         <v>337</v>
-      </c>
-      <c r="L35" t="n">
-        <v>284.9385014395953</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -37490,19 +37490,19 @@
         <v>140.2747533519553</v>
       </c>
       <c r="D37" t="n">
-        <v>127.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>103.2799843738239</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>138.6171440322581</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>168.0769468306011</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>185.3030706196928</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
@@ -37511,7 +37511,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>138.5162753791848</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
         <v>7.414962006155253</v>
@@ -37535,19 +37535,19 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>52.73207767419375</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>203.491663001939</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>21.49601948369172</v>
       </c>
       <c r="V37" t="n">
-        <v>213.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>186.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
         <v>165.5563545698924</v>
@@ -37587,28 +37587,28 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>337</v>
       </c>
       <c r="K38" t="n">
+        <v>34.26191457286433</v>
+      </c>
+      <c r="L38" t="n">
+        <v>250.6765868667309</v>
+      </c>
+      <c r="M38" t="n">
         <v>337</v>
       </c>
-      <c r="L38" t="n">
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>38.44533694424321</v>
+      </c>
+      <c r="Q38" t="n">
         <v>337</v>
-      </c>
-      <c r="M38" t="n">
-        <v>323.3838383838383</v>
-      </c>
-      <c r="N38" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>337</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>0</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -37672,7 +37672,7 @@
         <v>214.3749772823007</v>
       </c>
       <c r="L39" t="n">
-        <v>268.6811550412279</v>
+        <v>305.3822715751021</v>
       </c>
       <c r="M39" t="n">
         <v>123.4650421645043</v>
@@ -37684,7 +37684,7 @@
         <v>275.7452200159539</v>
       </c>
       <c r="P39" t="n">
-        <v>141.1853064014457</v>
+        <v>104.4841898675713</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -37724,7 +37724,7 @@
         <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>140.2747533519553</v>
       </c>
       <c r="D40" t="n">
         <v>0</v>
@@ -37733,13 +37733,13 @@
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>138.6171440322581</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>153.3485540300878</v>
       </c>
       <c r="H40" t="n">
-        <v>81.00241001352217</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
         <v>239.9999214290621</v>
@@ -37751,7 +37751,7 @@
         <v>138.5162753791848</v>
       </c>
       <c r="L40" t="n">
-        <v>7.414962006155253</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
@@ -37772,7 +37772,7 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>52.73207767419375</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -37787,10 +37787,10 @@
         <v>186.6271901612903</v>
       </c>
       <c r="X40" t="n">
-        <v>165.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>125.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -37824,19 +37824,19 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>337</v>
       </c>
       <c r="K41" t="n">
         <v>337</v>
       </c>
       <c r="L41" t="n">
-        <v>337</v>
+        <v>284.9385014395953</v>
       </c>
       <c r="M41" t="n">
-        <v>284.9385014395952</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>337</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -37845,7 +37845,7 @@
         <v>38.44533694424321</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>337</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -37964,7 +37964,7 @@
         <v>40.27475335195533</v>
       </c>
       <c r="D43" t="n">
-        <v>22.32968637443521</v>
+        <v>27.46378194444452</v>
       </c>
       <c r="E43" t="n">
         <v>32.01909516304346</v>
@@ -37976,7 +37976,7 @@
         <v>68.07694683060112</v>
       </c>
       <c r="H43" t="n">
-        <v>85.30307061969286</v>
+        <v>80.16897504968357</v>
       </c>
       <c r="I43" t="n">
         <v>139.9999214290621</v>
@@ -38064,16 +38064,16 @@
         <v>337</v>
       </c>
       <c r="K44" t="n">
+        <v>34.26191457286433</v>
+      </c>
+      <c r="L44" t="n">
+        <v>42.50493467336685</v>
+      </c>
+      <c r="M44" t="n">
         <v>337</v>
       </c>
-      <c r="L44" t="n">
-        <v>284.9385014395953</v>
-      </c>
-      <c r="M44" t="n">
-        <v>0</v>
-      </c>
       <c r="N44" t="n">
-        <v>337</v>
+        <v>208.1716521933641</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -38082,7 +38082,7 @@
         <v>38.44533694424321</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>337</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -38140,13 +38140,13 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>102.1230274396506</v>
+        <v>138.8241439735248</v>
       </c>
       <c r="K45" t="n">
         <v>214.3749772823007</v>
       </c>
       <c r="L45" t="n">
-        <v>305.3822715751021</v>
+        <v>268.6811550412279</v>
       </c>
       <c r="M45" t="n">
         <v>123.4650421645043</v>
